--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="14640" firstSheet="1" activeTab="7"/>
+    <workbookView windowWidth="29100" windowHeight="14640" tabRatio="719" firstSheet="7" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="设计规则" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="pms_op_log" sheetId="11" r:id="rId11"/>
     <sheet name="pms_access_log" sheetId="12" r:id="rId12"/>
     <sheet name="pms_user_preference" sheetId="13" r:id="rId13"/>
+    <sheet name="pms_message" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="395">
   <si>
     <t>规则项</t>
   </si>
@@ -266,6 +267,15 @@
     <t>用户默认进入页面、列表默认条数和外观兼容配置。</t>
   </si>
   <si>
+    <t>pms_message</t>
+  </si>
+  <si>
+    <t>消息表</t>
+  </si>
+  <si>
+    <t>后台通知和系统消息，记录接收人、消息类型、已读状态和跳转路径。</t>
+  </si>
+  <si>
     <t>pms_user（用户表）</t>
   </si>
   <si>
@@ -1146,6 +1156,75 @@
   </si>
   <si>
     <t>同一用户只能有一条偏好设置。</t>
+  </si>
+  <si>
+    <t>pms_message（消息表）</t>
+  </si>
+  <si>
+    <t>接收用户ID</t>
+  </si>
+  <si>
+    <t>recipient_user_id</t>
+  </si>
+  <si>
+    <t>接收消息的用户。</t>
+  </si>
+  <si>
+    <t>消息类型</t>
+  </si>
+  <si>
+    <t>notification</t>
+  </si>
+  <si>
+    <t>notification 通知，system 系统消息。</t>
+  </si>
+  <si>
+    <t>消息标题</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>VARCHAR(120)</t>
+  </si>
+  <si>
+    <t>工单明细导出完成</t>
+  </si>
+  <si>
+    <t>消息标题。</t>
+  </si>
+  <si>
+    <t>消息描述</t>
+  </si>
+  <si>
+    <t>导出文件已生成，可前往相关页面查看结果。</t>
+  </si>
+  <si>
+    <t>消息正文描述。</t>
+  </si>
+  <si>
+    <t>跳转路径</t>
+  </si>
+  <si>
+    <t>link_path</t>
+  </si>
+  <si>
+    <t>点击消息后跳转的前端路由，可为空。</t>
+  </si>
+  <si>
+    <t>已读时间</t>
+  </si>
+  <si>
+    <t>read_at</t>
+  </si>
+  <si>
+    <t>2026-07-05 17:30:00</t>
+  </si>
+  <si>
+    <t>已读时间；NULL 表示未读。</t>
+  </si>
+  <si>
+    <t>消息创建人或触发人。</t>
   </si>
 </sst>
 </file>
@@ -1830,7 +1909,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1862,14 +1941,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="49" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1933,19 +2006,7 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
     <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2139,25 +2200,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="10"/>
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstColumn" dxfId="7"/>
-      <tableStyleElement type="lastColumn" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="4"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
-      <tableStyleElement type="pageFieldValues" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2169,12 +2230,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableList" displayName="TableList" ref="A1:D11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TableList" displayName="TableList" ref="A1:D12" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" name="序号" dataDxfId="0"/>
-    <tableColumn id="2" name="表名" dataDxfId="1"/>
-    <tableColumn id="3" name="中文名称" dataDxfId="2"/>
-    <tableColumn id="4" name="说明" dataDxfId="3"/>
+    <tableColumn id="1" name="序号"/>
+    <tableColumn id="2" name="表名"/>
+    <tableColumn id="3" name="中文名称"/>
+    <tableColumn id="4" name="说明"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2378,152 +2439,152 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="96.4632352941177" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="18" style="17" customWidth="1"/>
-    <col min="2" max="2" width="44" style="17" customWidth="1"/>
-    <col min="3" max="3" width="80" style="17" customWidth="1"/>
-    <col min="4" max="16384" width="96.4632352941177" style="17" customWidth="1"/>
+    <col min="1" max="1" width="18" style="15" customWidth="1"/>
+    <col min="2" max="2" width="44" style="15" customWidth="1"/>
+    <col min="3" max="3" width="80" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="96.4632352941177" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A1" s="18" t="s">
+    <row r="1" s="14" customFormat="1" ht="17" customHeight="1" spans="1:3">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="17" customHeight="1" spans="1:3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2564,7 +2625,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2578,328 +2639,328 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="8">
         <v>1</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I7" s="8">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I8" s="8">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I10" s="8">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2932,7 +2993,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2946,312 +3007,312 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I7" s="8">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3284,7 +3345,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3298,274 +3359,274 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="8" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>317</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>31</v>
@@ -3575,21 +3636,21 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>31</v>
@@ -3599,21 +3660,21 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:10">
       <c r="A14" s="9" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>31</v>
@@ -3623,115 +3684,115 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I15" s="10">
         <v>3600</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:10">
       <c r="A17" s="9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:10">
       <c r="A18" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3764,7 +3825,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3778,134 +3839,134 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
@@ -3917,85 +3978,85 @@
         <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
@@ -4015,29 +4076,409 @@
         <v>24</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H11" s="7"/>
       <c r="I11" s="8" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr defaultColWidth="55.7647058823529" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="8.97058823529412" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.6764705882353" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.6470588235294" style="2" customWidth="1"/>
+    <col min="4" max="4" width="4.11764705882353" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.35294117647059" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.85294117647059" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.35294117647059" style="2" customWidth="1"/>
+    <col min="8" max="8" width="5.73529411764706" style="2" customWidth="1"/>
+    <col min="9" max="9" width="33.6764705882353" style="2" customWidth="1"/>
+    <col min="10" max="10" width="28.9705882352941" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="55.7647058823529" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A4" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8">
+        <v>1</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A5" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A6" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A7" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A8" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A9" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A10" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A12" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
+      <c r="A13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4052,182 +4493,196 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="4.70588235294118" style="13" customWidth="1"/>
-    <col min="2" max="2" width="18.6470588235294" style="13" customWidth="1"/>
-    <col min="3" max="3" width="13.2352941176471" style="13" customWidth="1"/>
-    <col min="4" max="4" width="45.8235294117647" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="13" customWidth="1"/>
+    <col min="1" max="1" width="4.70588235294118" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6470588235294" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.2352941176471" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.7058823529412" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="1" spans="1:4">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="15">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="15">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="15">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="15">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="15">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="15">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="15">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="15">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="15">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="15">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="15">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="9" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4260,7 +4715,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4274,156 +4729,156 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -4433,193 +4888,193 @@
         <v>34</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I8" s="8">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>112</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I9" s="8">
         <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I10" s="8">
         <v>1</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I11" s="8">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4652,7 +5107,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4666,272 +5121,272 @@
     </row>
     <row r="2" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I7" s="8">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I8" s="8">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I9" s="8">
         <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" s="11" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4964,7 +5419,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4978,150 +5433,150 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="8">
         <v>1</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -5141,29 +5596,29 @@
         <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -5196,7 +5651,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5210,404 +5665,404 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I4" s="8">
         <v>0</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I7" s="8">
         <v>2</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I10" s="8">
         <v>10</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I11" s="8">
         <v>1</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I12" s="9">
         <v>1</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I13" s="9">
         <v>1</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I14" s="9">
         <v>0</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -5640,7 +6095,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5654,150 +6109,150 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="8">
         <v>5</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:10">
@@ -5817,29 +6272,29 @@
         <v>24</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="8" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -5872,7 +6327,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5886,284 +6341,284 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8">
         <v>1</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="8">
         <v>4</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="8" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>213</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="8">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I10" s="8">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:10">
       <c r="A12" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>31</v>
@@ -6173,21 +6628,21 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>31</v>
@@ -6197,21 +6652,21 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="9" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>31</v>
@@ -6221,217 +6676,217 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="9" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
       <c r="I17" s="9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I18" s="9">
         <v>1</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="9" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I19" s="9">
         <v>1</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I20" s="9">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -6464,7 +6919,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -6478,302 +6933,302 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A3" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I3" s="8">
         <v>1</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A4" s="7" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H4" s="7"/>
       <c r="I4" s="8" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A5" s="7" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A6" s="7" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="8" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I7" s="8">
         <v>1</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A8" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I8" s="8">
         <v>1</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A9" s="7" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="8">
         <v>1</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A10" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="I10" s="8">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="1:10">
       <c r="A11" s="7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:10">
       <c r="A12" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,20 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rd40198d6f67f44f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R0239707e36184be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R2426dc62deb748b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rf4b784e5da244ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R237e65893a06434e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R56b778ce8e1f4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R38dbdf9f249c4ed9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="Rdcad48a3d8e94dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R5a2e20d2154a47c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R43b3fbbea4404882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R24a613988c8b4a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Rd03b6ad23d484af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R63f0a904052e4e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Ra6082f9ea4f84b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rd30e3fa941b44403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R9a66996217124dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Rb0748ef8007d49e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rdd67fbce6e804a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R82eb2f18fc114b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Re04ccba0fe7c4d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R7434f07979934eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R60bedb98fa3d4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="Rb0e9625dfc6c49e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rc4b58edc76b0483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R25c88550db684b08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Rd6c2e05cbc3745d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="Rbb6ede752ec047a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R24e20227f7e64689"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2799,8 +2799,8 @@
     <x:col min="6" max="6" width="9.852941513061523" style="2" customWidth="1"/>
     <x:col min="7" max="7" width="7.352941036224365" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="6.411764621734619" style="2" customWidth="1"/>
-    <x:col min="9" max="9" width="19.117647171020508" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="13.970588684082031" style="2" customWidth="1"/>
+    <x:col min="9" max="9" width="34" style="2" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" style="2" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="55.764705657958984" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3103,28 +3103,54 @@
       </x:c>
     </x:row>
     <x:row r="13" s="1" customFormat="1">
-      <x:c r="A13" s="9" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="B13" s="9" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C13" s="9" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D13" s="9" t="s">
-        <x:v>90</x:v>
-      </x:c>
+      <x:c r="A13" s="9" t="str">
+        <x:v>操作批次ID</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="str">
+        <x:v>operation_id</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>UUID</x:v>
+      </x:c>
+      <x:c r="D13" s="9"/>
       <x:c r="E13" s="9"/>
       <x:c r="F13" s="9"/>
-      <x:c r="G13" s="9"/>
-      <x:c r="H13" s="9" t="s">
+      <x:c r="G13" s="9" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H13" s="9" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I13" s="9" t="str">
+        <x:v>550e8400-e29b-41d4-a716-446655440000</x:v>
+      </x:c>
+      <x:c r="J13" s="9" t="str">
+        <x:v>同一次业务操作共享，用于聚合多字段变更。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="I13" s="9" t="s">
+      <x:c r="I14" t="s">
         <x:v>135</x:v>
       </x:c>
-      <x:c r="J13" s="9" t="s">
+      <x:c r="J14" t="s">
         <x:v>301</x:v>
       </x:c>
     </x:row>
@@ -4489,7 +4515,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788f66b8ccf94cd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a184306063848ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,40 +2,40 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rb35da9756f984350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Rb7700a32638f47cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R4a15260e33f04492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R9443a6ca57964d58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R3ae8b78f86404db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Rb0742393523f4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rba4b3c39f2994290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R26f2b6150c7045b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="Rd18c1a5bd9b941ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="Re2dbe3e721ae4205"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rbde3895ecedd4767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R710658ada90f481b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Rf0c028e8a678404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="Re7f98d1fe5e14d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R72c5079bafb146a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="R9d27831bf5144ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Ra2e9cedf74b140b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="Rcb11aa36cddb4c86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Rf034c492f6944f3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rbdccd585d1754df6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R244859b92f184af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="Rbe28ac0e9e034802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R6c641dc8aee94f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R5cc03a0a4c7e4e1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="Re74046704e784cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R49b3f1d62c9a4a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R591af0f562eb4448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R18ada9413e564ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R5573f191ecd24d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R66a55a08bd8e425f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="Re79f9b32bcbf49c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="R96e81ffd2632468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="Redca729ceb1842ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="Re56dbe2bd2924d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R9f501ae045a24b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Rfd244a8b518a47fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R27b536af59f746df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Ra13e38fd7f27452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R177174f4687241ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Ra8fcbee39e774ad6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R36b7506f5ebb4357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="Rf261bd89074641b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R31eb362f750448d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R1f24709569374d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Re4c6311501c14499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Ra2f26813c5b44c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R47609e38b9ba4587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R10c3201cfe8f4314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Rfdca304d42a74004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="Rd7c7d4159eda44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="R4ec4fb873f8649dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R0162315b936e4972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="R32af2ab922d74a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="R4499722dd95d4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R38663b75e1e24001"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R3bd3e0fa231d4c2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="Re08d5dc61a834567"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R6fa6096b32de4da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="R11b5ba4401274f6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R6d4eed3b09a6497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R83ea5366d7ed4f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R7a6aa4c2435a49f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="Rf27d196f7b244fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R165b8279091541aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R281dd774c9284fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="R83db0e00e9f24cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R1a865e78416145f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R8485ca700b224b51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2162,12 +2162,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">文件记录 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">服务端随机存储键</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">storage_key</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">MIME 类型</x:t>
@@ -3171,7 +3165,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="FieldSummary" displayName="FieldSummary" ref="A4:N382" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="FieldSummary" displayName="FieldSummary" ref="A4:N383" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="表名"/>
@@ -7947,7 +7941,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13d526e36b004f87"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d1f88701ee4696"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11714,7 +11708,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>共汇总 31 张业务及系统表、379 个字段；全部明细 Sheet 统一使用 10 列字段模板。</x:v>
+        <x:v>共汇总 31 张业务及系统表、380 个字段；全部明细 Sheet 统一使用 10 列字段模板。</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -25947,20 +25941,40 @@
       </x:c>
     </x:row>
     <x:row r="383">
-      <x:c r="A383"/>
-      <x:c r="B383"/>
-      <x:c r="C383"/>
-      <x:c r="D383"/>
-      <x:c r="E383"/>
-      <x:c r="F383"/>
+      <x:c r="A383" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B383" t="str">
+        <x:v>pms_project_plan_delivery_file</x:v>
+      </x:c>
+      <x:c r="C383" t="str">
+        <x:v>关键事项交付文件表</x:v>
+      </x:c>
+      <x:c r="D383" t="str">
+        <x:v>OSS 上传响应</x:v>
+      </x:c>
+      <x:c r="E383" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="F383" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
       <x:c r="G383"/>
       <x:c r="H383"/>
       <x:c r="I383"/>
       <x:c r="J383"/>
-      <x:c r="K383"/>
-      <x:c r="L383"/>
-      <x:c r="M383"/>
-      <x:c r="N383"/>
+      <x:c r="K383" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L383" t="str">
+        <x:v>{"code":100}</x:v>
+      </x:c>
+      <x:c r="M383" t="str">
+        <x:v>OSS 上传接口完整响应；迁移前历史本地文件为空。</x:v>
+      </x:c>
+      <x:c r="N383" t="str">
+        <x:v>项目管理</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -25969,7 +25983,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e4dbf1d05404c4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R913cc5f88aa94836"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26347,62 +26361,66 @@
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>707</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>708</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="s">
-        <x:v>195</x:v>
+      <x:c r="A6" s="5" t="str">
+        <x:v>OSS 文件路径</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>storage_key</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>有效数据唯一</x:v>
       </x:c>
       <x:c r="F6" s="5"/>
-      <x:c r="G6" s="6" t="s">
-        <x:v>137</x:v>
+      <x:c r="G6" s="6" t="str">
+        <x:v>是</x:v>
       </x:c>
       <x:c r="H6" s="5"/>
-      <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5" t="s">
-        <x:v>707</x:v>
+      <x:c r="I6" s="5" t="str">
+        <x:v>pmis/...</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="str">
+        <x:v>OSS 文件路径；迁移前历史数据为本地随机存储键。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>709</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>654</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>655</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="A7" s="5" t="str">
+        <x:v>OSS 上传响应</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="D7" s="6"/>
       <x:c r="E7" s="6"/>
       <x:c r="F7" s="5"/>
       <x:c r="G7" s="6"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
-      <x:c r="J7" s="5" t="s">
-        <x:v>709</x:v>
+      <x:c r="H7" s="5" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
+        <x:v>{"code":100}</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="str">
+        <x:v>OSS 上传接口完整响应；迁移前历史本地文件为空。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>658</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>710</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>137</x:v>
@@ -26413,18 +26431,18 @@
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5" t="s">
-        <x:v>658</x:v>
+        <x:v>707</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>711</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>712</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>241</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
         <x:v>137</x:v>
@@ -26432,66 +26450,64 @@
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="5"/>
       <x:c r="G9" s="6"/>
-      <x:c r="H9" s="5">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>711</x:v>
+        <x:v>658</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.399999618530273" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>713</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>714</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D10" s="6"/>
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E10" s="6"/>
-      <x:c r="F10" s="5" t="s">
-        <x:v>715</x:v>
-      </x:c>
+      <x:c r="F10" s="5"/>
       <x:c r="G10" s="6"/>
-      <x:c r="H10" s="5"/>
+      <x:c r="H10" s="5">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5" t="s">
-        <x:v>716</x:v>
+        <x:v>709</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>717</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>718</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
-      <x:c r="F11" s="5"/>
+      <x:c r="F11" s="5" t="s">
+        <x:v>713</x:v>
+      </x:c>
       <x:c r="G11" s="6"/>
-      <x:c r="H11" s="5">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5" t="s">
-        <x:v>717</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="12" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>719</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>720</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
         <x:v>161</x:v>
@@ -26503,79 +26519,103 @@
       <x:c r="F12" s="5"/>
       <x:c r="G12" s="6"/>
       <x:c r="H12" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5" t="s">
-        <x:v>719</x:v>
+        <x:v>715</x:v>
       </x:c>
     </x:row>
     <x:row r="13" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>721</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>722</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="D13" s="6"/>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E13" s="6"/>
       <x:c r="F13" s="5"/>
       <x:c r="G13" s="6"/>
-      <x:c r="H13" s="5"/>
+      <x:c r="H13" s="5">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5" t="s">
-        <x:v>723</x:v>
+        <x:v>717</x:v>
       </x:c>
     </x:row>
     <x:row r="14" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>724</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>725</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D14" s="6"/>
       <x:c r="E14" s="6"/>
-      <x:c r="F14" s="5" t="s">
-        <x:v>170</x:v>
-      </x:c>
+      <x:c r="F14" s="5"/>
       <x:c r="G14" s="6"/>
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="5" t="s">
-        <x:v>726</x:v>
+        <x:v>721</x:v>
       </x:c>
     </x:row>
     <x:row r="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>181</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D15" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D15" s="6"/>
       <x:c r="E15" s="6"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H15" s="5" t="s">
-        <x:v>182</x:v>
-      </x:c>
+      <x:c r="F15" s="5" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G15" s="6"/>
+      <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5" t="s">
-        <x:v>727</x:v>
+        <x:v>724</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H16" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I16"/>
+      <x:c r="J16" t="s">
+        <x:v>725</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26996,7 +27036,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad01bfacc3e0494b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b1af2e5dea4f7a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27575,7 +27615,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e3362a007894e6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0fa2c97b514e1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27986,7 +28026,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b8ad646edf646ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3adcf8ad7fa548bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,40 +2,43 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R9f501ae045a24b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Rfd244a8b518a47fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R27b536af59f746df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="Ra13e38fd7f27452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R177174f4687241ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="Ra8fcbee39e774ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R36b7506f5ebb4357"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="Rf261bd89074641b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R31eb362f750448d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R1f24709569374d00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Re4c6311501c14499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Ra2f26813c5b44c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R47609e38b9ba4587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R10c3201cfe8f4314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Rfdca304d42a74004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="Rd7c7d4159eda44c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="R4ec4fb873f8649dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R0162315b936e4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="R32af2ab922d74a12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="R4499722dd95d4941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R38663b75e1e24001"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R3bd3e0fa231d4c2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="Re08d5dc61a834567"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R6fa6096b32de4da1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="R11b5ba4401274f6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R6d4eed3b09a6497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R83ea5366d7ed4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R7a6aa4c2435a49f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="Rf27d196f7b244fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R165b8279091541aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R281dd774c9284fdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="R83db0e00e9f24cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R1a865e78416145f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R8485ca700b224b51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rbec888e06b6f476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R9093d359b9fc4ebd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R797808f789fc4eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R8ccfc2a8f2114a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Radc85e9c1d354474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R0ef10c2b06a74f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rb282f17dbcbd4499"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R6c601ef8560244bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R30bf89e7cdd6478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R28b61dacacc04b44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Red65d44f112549ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R63a4332c11ad44e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R6d21670fff6e465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R32101a24c5484bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Re41421f691ca4442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="Rff618688102e4a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rf5f5108036f84d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R6e9c2358bd6d441d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Re1926a60086f4a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rfcfc681d596745cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="Rc3764fc9a339426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R110aee2926b34225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R2c20c2a305c24869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R6c06b5c897ed48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="R063507d1793243e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R4f9a118f5e39414a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R622c3eb50daa4192"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R8e5b57b8bbf94145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R9c9a3efd53884c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R1b120b9cc3e2412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R96c733a4a16148e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="Rfdb25040e02c4cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R411834331b1f49cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R15d6b180c4604710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="R2381bbc29a0648be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="Rf7b3fbc2479045dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="Rb0a53faeeae34fa2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2842,7 +2845,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
@@ -2915,6 +2918,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -3153,7 +3159,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="TableInventory" displayName="TableInventory" ref="A1:D32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="TableInventory" displayName="TableInventory" ref="A1:D35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="表名"/>
@@ -3165,7 +3171,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="FieldSummary" displayName="FieldSummary" ref="A4:N383" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="FieldSummary" displayName="FieldSummary" ref="A4:N407" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="表名"/>
@@ -3224,6 +3230,60 @@
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="pmsmcpactionticketTable" displayName="pmsmcpactionticketTable" ref="A2:J15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="中文字段名"/>
+    <x:tableColumn id="2" name="技术字段名"/>
+    <x:tableColumn id="3" name="数据类型"/>
+    <x:tableColumn id="4" name="必填"/>
+    <x:tableColumn id="5" name="是否唯一"/>
+    <x:tableColumn id="6" name="关联引用"/>
+    <x:tableColumn id="7" name="是否索引"/>
+    <x:tableColumn id="8" name="默认值"/>
+    <x:tableColumn id="9" name="示例"/>
+    <x:tableColumn id="10" name="字段说明"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="ProjectPlanTemplateTable1" displayName="ProjectPlanTemplateTable1" ref="A2:J10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="中文字段名"/>
+    <x:tableColumn id="2" name="技术字段名"/>
+    <x:tableColumn id="3" name="数据类型"/>
+    <x:tableColumn id="4" name="必填"/>
+    <x:tableColumn id="5" name="是否唯一"/>
+    <x:tableColumn id="6" name="关联引用"/>
+    <x:tableColumn id="7" name="是否索引"/>
+    <x:tableColumn id="8" name="默认值"/>
+    <x:tableColumn id="9" name="示例"/>
+    <x:tableColumn id="10" name="字段说明"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="ProjectPlanTemplateTable2" displayName="ProjectPlanTemplateTable2" ref="A2:J9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="中文字段名"/>
+    <x:tableColumn id="2" name="技术字段名"/>
+    <x:tableColumn id="3" name="数据类型"/>
+    <x:tableColumn id="4" name="必填"/>
+    <x:tableColumn id="5" name="是否唯一"/>
+    <x:tableColumn id="6" name="关联引用"/>
+    <x:tableColumn id="7" name="是否索引"/>
+    <x:tableColumn id="8" name="默认值"/>
+    <x:tableColumn id="9" name="示例"/>
+    <x:tableColumn id="10" name="字段说明"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="ProjectPlanTemplateTable3" displayName="ProjectPlanTemplateTable3" ref="A2:J11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="中文字段名"/>
     <x:tableColumn id="2" name="技术字段名"/>
@@ -7938,10 +7998,52 @@
         <x:v>保存五分钟有效的一次性操作预览、参数哈希和幂等键。</x:v>
       </x:c>
     </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>模板编码、名称、启停状态和顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>模板内的阶段定义和顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>模板阶段内的关键事项和交付要求。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d1f88701ee4696"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60f8413ff0d945cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11708,7 +11810,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>共汇总 31 张业务及系统表、380 个字段；全部明细 Sheet 统一使用 10 列字段模板。</x:v>
+        <x:v>共汇总 34 张业务及系统表、403 个字段；全部明细 Sheet 统一使用 10 列字段模板。</x:v>
       </x:c>
       <x:c r="B2" s="12"/>
       <x:c r="C2" s="12"/>
@@ -25976,6 +26078,888 @@
         <x:v>项目管理</x:v>
       </x:c>
     </x:row>
+    <x:row r="384">
+      <x:c r="A384" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B384" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C384" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D384" t="str">
+        <x:v>模板ID</x:v>
+      </x:c>
+      <x:c r="E384" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F384" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G384" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H384" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I384"/>
+      <x:c r="J384" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K384" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L384" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M384" t="str">
+        <x:v>模板主键。</x:v>
+      </x:c>
+      <x:c r="N384"/>
+    </x:row>
+    <x:row r="385">
+      <x:c r="A385" t="n">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B385" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C385" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D385" t="str">
+        <x:v>模板编码</x:v>
+      </x:c>
+      <x:c r="E385" t="str">
+        <x:v>code</x:v>
+      </x:c>
+      <x:c r="F385" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="G385" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H385" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I385"/>
+      <x:c r="J385" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K385"/>
+      <x:c r="L385" t="str">
+        <x:v>ai_project_standard</x:v>
+      </x:c>
+      <x:c r="M385" t="str">
+        <x:v>模板稳定编码，全局唯一。</x:v>
+      </x:c>
+      <x:c r="N385"/>
+    </x:row>
+    <x:row r="386">
+      <x:c r="A386" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B386" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C386" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D386" t="str">
+        <x:v>模板名称</x:v>
+      </x:c>
+      <x:c r="E386" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="F386" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="G386" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H386"/>
+      <x:c r="I386"/>
+      <x:c r="J386"/>
+      <x:c r="K386"/>
+      <x:c r="L386" t="str">
+        <x:v>AI 项目标准模板</x:v>
+      </x:c>
+      <x:c r="M386" t="str">
+        <x:v>模板显示名称。</x:v>
+      </x:c>
+      <x:c r="N386"/>
+    </x:row>
+    <x:row r="387">
+      <x:c r="A387" t="n">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B387" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C387" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D387" t="str">
+        <x:v>模板说明</x:v>
+      </x:c>
+      <x:c r="E387" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="F387" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G387"/>
+      <x:c r="H387"/>
+      <x:c r="I387"/>
+      <x:c r="J387"/>
+      <x:c r="K387" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L387" t="str">
+        <x:v>AI 项目从立项到验收的标准阶段主计划</x:v>
+      </x:c>
+      <x:c r="M387" t="str">
+        <x:v>模板用途说明。</x:v>
+      </x:c>
+      <x:c r="N387"/>
+    </x:row>
+    <x:row r="388">
+      <x:c r="A388" t="n">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B388" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C388" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D388" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="E388" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="F388" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G388" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H388"/>
+      <x:c r="I388"/>
+      <x:c r="J388" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K388" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L388" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M388" t="str">
+        <x:v>1 启用，0 停用。</x:v>
+      </x:c>
+      <x:c r="N388"/>
+    </x:row>
+    <x:row r="389">
+      <x:c r="A389" t="n">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B389" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C389" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D389" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="E389" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="F389" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G389" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H389"/>
+      <x:c r="I389"/>
+      <x:c r="J389" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K389" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L389" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M389" t="str">
+        <x:v>模板显示顺序。</x:v>
+      </x:c>
+      <x:c r="N389"/>
+    </x:row>
+    <x:row r="390">
+      <x:c r="A390" t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B390" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C390" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D390" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E390" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F390" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G390" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H390"/>
+      <x:c r="I390"/>
+      <x:c r="J390"/>
+      <x:c r="K390" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L390" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M390" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+      <x:c r="N390"/>
+    </x:row>
+    <x:row r="391">
+      <x:c r="A391" t="n">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B391" t="str">
+        <x:v>pms_project_plan_template</x:v>
+      </x:c>
+      <x:c r="C391" t="str">
+        <x:v>阶段主计划模板表</x:v>
+      </x:c>
+      <x:c r="D391" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E391" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F391" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G391" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H391"/>
+      <x:c r="I391"/>
+      <x:c r="J391"/>
+      <x:c r="K391" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L391" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M391" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N391"/>
+    </x:row>
+    <x:row r="392">
+      <x:c r="A392" t="n">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B392" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C392" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D392" t="str">
+        <x:v>模板阶段ID</x:v>
+      </x:c>
+      <x:c r="E392" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F392" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G392" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H392" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I392"/>
+      <x:c r="J392" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K392" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L392" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M392" t="str">
+        <x:v>模板阶段主键。</x:v>
+      </x:c>
+      <x:c r="N392"/>
+    </x:row>
+    <x:row r="393">
+      <x:c r="A393" t="n">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B393" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C393" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D393" t="str">
+        <x:v>模板ID</x:v>
+      </x:c>
+      <x:c r="E393" t="str">
+        <x:v>template_id</x:v>
+      </x:c>
+      <x:c r="F393" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G393" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H393" t="str">
+        <x:v>同模板名称唯一</x:v>
+      </x:c>
+      <x:c r="I393" t="str">
+        <x:v>pms_project_plan_template.id</x:v>
+      </x:c>
+      <x:c r="J393" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K393"/>
+      <x:c r="L393" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M393" t="str">
+        <x:v>所属模板，模板删除时级联删除。</x:v>
+      </x:c>
+      <x:c r="N393"/>
+    </x:row>
+    <x:row r="394">
+      <x:c r="A394" t="n">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B394" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C394" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D394" t="str">
+        <x:v>阶段名称</x:v>
+      </x:c>
+      <x:c r="E394" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="F394" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="G394" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H394" t="str">
+        <x:v>同模板名称唯一</x:v>
+      </x:c>
+      <x:c r="I394"/>
+      <x:c r="J394"/>
+      <x:c r="K394"/>
+      <x:c r="L394" t="str">
+        <x:v>项目立项</x:v>
+      </x:c>
+      <x:c r="M394" t="str">
+        <x:v>模板阶段名称。</x:v>
+      </x:c>
+      <x:c r="N394"/>
+    </x:row>
+    <x:row r="395">
+      <x:c r="A395" t="n">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B395" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C395" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D395" t="str">
+        <x:v>阶段说明</x:v>
+      </x:c>
+      <x:c r="E395" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="F395" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G395"/>
+      <x:c r="H395"/>
+      <x:c r="I395"/>
+      <x:c r="J395"/>
+      <x:c r="K395" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L395"/>
+      <x:c r="M395" t="str">
+        <x:v>模板阶段说明。</x:v>
+      </x:c>
+      <x:c r="N395"/>
+    </x:row>
+    <x:row r="396">
+      <x:c r="A396" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B396" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C396" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D396" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="E396" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="F396" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G396" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H396"/>
+      <x:c r="I396"/>
+      <x:c r="J396" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K396" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L396" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M396" t="str">
+        <x:v>模板内阶段顺序。</x:v>
+      </x:c>
+      <x:c r="N396"/>
+    </x:row>
+    <x:row r="397">
+      <x:c r="A397" t="n">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B397" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C397" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D397" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E397" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F397" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G397" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H397"/>
+      <x:c r="I397"/>
+      <x:c r="J397"/>
+      <x:c r="K397" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L397" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M397" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+      <x:c r="N397"/>
+    </x:row>
+    <x:row r="398">
+      <x:c r="A398" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B398" t="str">
+        <x:v>pms_project_plan_template_stage</x:v>
+      </x:c>
+      <x:c r="C398" t="str">
+        <x:v>阶段主计划模板阶段表</x:v>
+      </x:c>
+      <x:c r="D398" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E398" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F398" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G398" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H398"/>
+      <x:c r="I398"/>
+      <x:c r="J398"/>
+      <x:c r="K398" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L398" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M398" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N398"/>
+    </x:row>
+    <x:row r="399">
+      <x:c r="A399" t="n">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B399" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C399" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D399" t="str">
+        <x:v>模板事项ID</x:v>
+      </x:c>
+      <x:c r="E399" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F399" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G399" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H399" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I399"/>
+      <x:c r="J399" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K399" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L399" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M399" t="str">
+        <x:v>模板事项主键。</x:v>
+      </x:c>
+      <x:c r="N399"/>
+    </x:row>
+    <x:row r="400">
+      <x:c r="A400" t="n">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B400" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C400" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D400" t="str">
+        <x:v>模板阶段ID</x:v>
+      </x:c>
+      <x:c r="E400" t="str">
+        <x:v>template_stage_id</x:v>
+      </x:c>
+      <x:c r="F400" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G400" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H400" t="str">
+        <x:v>同阶段名称唯一</x:v>
+      </x:c>
+      <x:c r="I400" t="str">
+        <x:v>pms_project_plan_template_stage.id</x:v>
+      </x:c>
+      <x:c r="J400" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K400"/>
+      <x:c r="L400" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M400" t="str">
+        <x:v>所属模板阶段，阶段删除时级联删除。</x:v>
+      </x:c>
+      <x:c r="N400"/>
+    </x:row>
+    <x:row r="401">
+      <x:c r="A401" t="n">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B401" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C401" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D401" t="str">
+        <x:v>关键事项名称</x:v>
+      </x:c>
+      <x:c r="E401" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="F401" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="G401" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H401" t="str">
+        <x:v>同阶段名称唯一</x:v>
+      </x:c>
+      <x:c r="I401"/>
+      <x:c r="J401"/>
+      <x:c r="K401"/>
+      <x:c r="L401" t="str">
+        <x:v>立项汇报</x:v>
+      </x:c>
+      <x:c r="M401" t="str">
+        <x:v>模板关键事项名称。</x:v>
+      </x:c>
+      <x:c r="N401"/>
+    </x:row>
+    <x:row r="402">
+      <x:c r="A402" t="n">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B402" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C402" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D402" t="str">
+        <x:v>需要交付文件</x:v>
+      </x:c>
+      <x:c r="E402" t="str">
+        <x:v>requires_delivery_file</x:v>
+      </x:c>
+      <x:c r="F402" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G402" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H402"/>
+      <x:c r="I402"/>
+      <x:c r="J402"/>
+      <x:c r="K402" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L402" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M402" t="str">
+        <x:v>1 需要关键交付文件，0 不需要。</x:v>
+      </x:c>
+      <x:c r="N402"/>
+    </x:row>
+    <x:row r="403">
+      <x:c r="A403" t="n">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B403" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C403" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D403" t="str">
+        <x:v>交付文件要求</x:v>
+      </x:c>
+      <x:c r="E403" t="str">
+        <x:v>delivery_requirement</x:v>
+      </x:c>
+      <x:c r="F403" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G403" t="str">
+        <x:v>条件必填</x:v>
+      </x:c>
+      <x:c r="H403"/>
+      <x:c r="I403"/>
+      <x:c r="J403"/>
+      <x:c r="K403" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L403" t="str">
+        <x:v>关键交付文件</x:v>
+      </x:c>
+      <x:c r="M403" t="str">
+        <x:v>需要交付文件时必填。</x:v>
+      </x:c>
+      <x:c r="N403"/>
+    </x:row>
+    <x:row r="404">
+      <x:c r="A404" t="n">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B404" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C404" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D404" t="str">
+        <x:v>默认备注</x:v>
+      </x:c>
+      <x:c r="E404" t="str">
+        <x:v>remark</x:v>
+      </x:c>
+      <x:c r="F404" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G404"/>
+      <x:c r="H404"/>
+      <x:c r="I404"/>
+      <x:c r="J404"/>
+      <x:c r="K404" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L404"/>
+      <x:c r="M404" t="str">
+        <x:v>生成关键事项时使用的默认备注。</x:v>
+      </x:c>
+      <x:c r="N404"/>
+    </x:row>
+    <x:row r="405">
+      <x:c r="A405" t="n">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B405" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C405" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D405" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="E405" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="F405" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G405" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H405"/>
+      <x:c r="I405"/>
+      <x:c r="J405" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K405" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L405" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M405" t="str">
+        <x:v>模板阶段内事项顺序。</x:v>
+      </x:c>
+      <x:c r="N405"/>
+    </x:row>
+    <x:row r="406">
+      <x:c r="A406" t="n">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B406" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C406" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D406" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E406" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F406" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G406" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H406"/>
+      <x:c r="I406"/>
+      <x:c r="J406"/>
+      <x:c r="K406" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L406" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M406" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+      <x:c r="N406"/>
+    </x:row>
+    <x:row r="407">
+      <x:c r="A407" t="n">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B407" t="str">
+        <x:v>pms_project_plan_template_item</x:v>
+      </x:c>
+      <x:c r="C407" t="str">
+        <x:v>阶段主计划模板事项表</x:v>
+      </x:c>
+      <x:c r="D407" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E407" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F407" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G407" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H407"/>
+      <x:c r="I407"/>
+      <x:c r="J407"/>
+      <x:c r="K407" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L407" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="M407" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N407"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
@@ -25983,7 +26967,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R913cc5f88aa94836"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R594081a923d54890"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27036,7 +28020,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b1af2e5dea4f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9729e2913c604d0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27615,7 +28599,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0fa2c97b514e1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf770be862a5f43d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28026,7 +29010,868 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3adcf8ad7fa548bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f10298c546e414b"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="29" t="str">
+        <x:v>pms_project_plan_template（阶段主计划模板表）</x:v>
+      </x:c>
+      <x:c r="B1" s="29"/>
+      <x:c r="C1" s="29"/>
+      <x:c r="D1" s="29"/>
+      <x:c r="E1" s="29"/>
+      <x:c r="F1" s="29"/>
+      <x:c r="G1" s="29"/>
+      <x:c r="H1" s="29"/>
+      <x:c r="I1" s="29"/>
+      <x:c r="J1" s="29"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="29" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="29" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="29" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="29" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="29" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="29" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="29" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="29" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="29" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="29" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="29" t="str">
+        <x:v>模板ID</x:v>
+      </x:c>
+      <x:c r="B3" s="29" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="29" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="29"/>
+      <x:c r="G3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="29" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="29" t="str">
+        <x:v>模板主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="29" t="str">
+        <x:v>模板编码</x:v>
+      </x:c>
+      <x:c r="B4" s="29" t="str">
+        <x:v>code</x:v>
+      </x:c>
+      <x:c r="C4" s="29" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="D4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F4" s="29"/>
+      <x:c r="G4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="29"/>
+      <x:c r="I4" s="29" t="str">
+        <x:v>ai_project_standard</x:v>
+      </x:c>
+      <x:c r="J4" s="29" t="str">
+        <x:v>模板稳定编码，全局唯一。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="29" t="str">
+        <x:v>模板名称</x:v>
+      </x:c>
+      <x:c r="B5" s="29" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C5" s="29" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="D5" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="29"/>
+      <x:c r="F5" s="29"/>
+      <x:c r="G5" s="29"/>
+      <x:c r="H5" s="29"/>
+      <x:c r="I5" s="29" t="str">
+        <x:v>AI 项目标准模板</x:v>
+      </x:c>
+      <x:c r="J5" s="29" t="str">
+        <x:v>模板显示名称。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="29" t="str">
+        <x:v>模板说明</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D6" s="29"/>
+      <x:c r="E6" s="29"/>
+      <x:c r="F6" s="29"/>
+      <x:c r="G6" s="29"/>
+      <x:c r="H6" s="29" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I6" s="29" t="str">
+        <x:v>AI 项目从立项到验收的标准阶段主计划</x:v>
+      </x:c>
+      <x:c r="J6" s="29" t="str">
+        <x:v>模板用途说明。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="29" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D7" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E7" s="29"/>
+      <x:c r="F7" s="29"/>
+      <x:c r="G7" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H7" s="29" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="29" t="str">
+        <x:v>1 启用，0 停用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="29" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D8" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="29"/>
+      <x:c r="F8" s="29"/>
+      <x:c r="G8" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H8" s="29" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J8" s="29" t="str">
+        <x:v>模板显示顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="29" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="29"/>
+      <x:c r="F9" s="29"/>
+      <x:c r="G9" s="29"/>
+      <x:c r="H9" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I9" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J9" s="29" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="29" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E10" s="29"/>
+      <x:c r="F10" s="29"/>
+      <x:c r="G10" s="29"/>
+      <x:c r="H10" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I10" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J10" s="29" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e2ecb461e304e08"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="29" t="str">
+        <x:v>pms_project_plan_template_stage（阶段主计划模板阶段表）</x:v>
+      </x:c>
+      <x:c r="B1" s="29"/>
+      <x:c r="C1" s="29"/>
+      <x:c r="D1" s="29"/>
+      <x:c r="E1" s="29"/>
+      <x:c r="F1" s="29"/>
+      <x:c r="G1" s="29"/>
+      <x:c r="H1" s="29"/>
+      <x:c r="I1" s="29"/>
+      <x:c r="J1" s="29"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="29" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="29" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="29" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="29" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="29" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="29" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="29" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="29" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="29" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="29" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="29" t="str">
+        <x:v>模板阶段ID</x:v>
+      </x:c>
+      <x:c r="B3" s="29" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="29" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="29"/>
+      <x:c r="G3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="29" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="29" t="str">
+        <x:v>模板阶段主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="29" t="str">
+        <x:v>模板ID</x:v>
+      </x:c>
+      <x:c r="B4" s="29" t="str">
+        <x:v>template_id</x:v>
+      </x:c>
+      <x:c r="C4" s="29" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="29" t="str">
+        <x:v>同模板名称唯一</x:v>
+      </x:c>
+      <x:c r="F4" s="29" t="str">
+        <x:v>pms_project_plan_template.id</x:v>
+      </x:c>
+      <x:c r="G4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="29"/>
+      <x:c r="I4" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="29" t="str">
+        <x:v>所属模板，模板删除时级联删除。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="29" t="str">
+        <x:v>阶段名称</x:v>
+      </x:c>
+      <x:c r="B5" s="29" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C5" s="29" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="D5" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="29" t="str">
+        <x:v>同模板名称唯一</x:v>
+      </x:c>
+      <x:c r="F5" s="29"/>
+      <x:c r="G5" s="29"/>
+      <x:c r="H5" s="29"/>
+      <x:c r="I5" s="29" t="str">
+        <x:v>项目立项</x:v>
+      </x:c>
+      <x:c r="J5" s="29" t="str">
+        <x:v>模板阶段名称。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="29" t="str">
+        <x:v>阶段说明</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="str">
+        <x:v>description</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D6" s="29"/>
+      <x:c r="E6" s="29"/>
+      <x:c r="F6" s="29"/>
+      <x:c r="G6" s="29"/>
+      <x:c r="H6" s="29" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I6" s="29"/>
+      <x:c r="J6" s="29" t="str">
+        <x:v>模板阶段说明。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="29" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D7" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E7" s="29"/>
+      <x:c r="F7" s="29"/>
+      <x:c r="G7" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H7" s="29" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I7" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J7" s="29" t="str">
+        <x:v>模板内阶段顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="29" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D8" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="29"/>
+      <x:c r="F8" s="29"/>
+      <x:c r="G8" s="29"/>
+      <x:c r="H8" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I8" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J8" s="29" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="29" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="29"/>
+      <x:c r="F9" s="29"/>
+      <x:c r="G9" s="29"/>
+      <x:c r="H9" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I9" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J9" s="29" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10cf648a2533420d"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="29" t="str">
+        <x:v>pms_project_plan_template_item（阶段主计划模板事项表）</x:v>
+      </x:c>
+      <x:c r="B1" s="29"/>
+      <x:c r="C1" s="29"/>
+      <x:c r="D1" s="29"/>
+      <x:c r="E1" s="29"/>
+      <x:c r="F1" s="29"/>
+      <x:c r="G1" s="29"/>
+      <x:c r="H1" s="29"/>
+      <x:c r="I1" s="29"/>
+      <x:c r="J1" s="29"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="29" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="29" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="29" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="29" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="29" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="29" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="29" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="29" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="29" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="29" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="29" t="str">
+        <x:v>模板事项ID</x:v>
+      </x:c>
+      <x:c r="B3" s="29" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="29" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="29"/>
+      <x:c r="G3" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="29" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="29" t="str">
+        <x:v>模板事项主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="29" t="str">
+        <x:v>模板阶段ID</x:v>
+      </x:c>
+      <x:c r="B4" s="29" t="str">
+        <x:v>template_stage_id</x:v>
+      </x:c>
+      <x:c r="C4" s="29" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="29" t="str">
+        <x:v>同阶段名称唯一</x:v>
+      </x:c>
+      <x:c r="F4" s="29" t="str">
+        <x:v>pms_project_plan_template_stage.id</x:v>
+      </x:c>
+      <x:c r="G4" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="29"/>
+      <x:c r="I4" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="29" t="str">
+        <x:v>所属模板阶段，阶段删除时级联删除。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="30" customHeight="1">
+      <x:c r="A5" s="29" t="str">
+        <x:v>关键事项名称</x:v>
+      </x:c>
+      <x:c r="B5" s="29" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="C5" s="29" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="D5" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="29" t="str">
+        <x:v>同阶段名称唯一</x:v>
+      </x:c>
+      <x:c r="F5" s="29"/>
+      <x:c r="G5" s="29"/>
+      <x:c r="H5" s="29"/>
+      <x:c r="I5" s="29" t="str">
+        <x:v>立项汇报</x:v>
+      </x:c>
+      <x:c r="J5" s="29" t="str">
+        <x:v>模板关键事项名称。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="29" t="str">
+        <x:v>需要交付文件</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="str">
+        <x:v>requires_delivery_file</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D6" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="29"/>
+      <x:c r="F6" s="29"/>
+      <x:c r="G6" s="29"/>
+      <x:c r="H6" s="29" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="29" t="str">
+        <x:v>1 需要关键交付文件，0 不需要。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="29" t="str">
+        <x:v>交付文件要求</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="str">
+        <x:v>delivery_requirement</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D7" s="29" t="str">
+        <x:v>条件必填</x:v>
+      </x:c>
+      <x:c r="E7" s="29"/>
+      <x:c r="F7" s="29"/>
+      <x:c r="G7" s="29"/>
+      <x:c r="H7" s="29" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I7" s="29" t="str">
+        <x:v>关键交付文件</x:v>
+      </x:c>
+      <x:c r="J7" s="29" t="str">
+        <x:v>需要交付文件时必填。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="29" t="str">
+        <x:v>默认备注</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="str">
+        <x:v>remark</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D8" s="29"/>
+      <x:c r="E8" s="29"/>
+      <x:c r="F8" s="29"/>
+      <x:c r="G8" s="29"/>
+      <x:c r="H8" s="29" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I8" s="29"/>
+      <x:c r="J8" s="29" t="str">
+        <x:v>生成关键事项时使用的默认备注。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="29" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="29"/>
+      <x:c r="F9" s="29"/>
+      <x:c r="G9" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H9" s="29" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="29" t="str">
+        <x:v>模板阶段内事项顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="29" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E10" s="29"/>
+      <x:c r="F10" s="29"/>
+      <x:c r="G10" s="29"/>
+      <x:c r="H10" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I10" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J10" s="29" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="30" customHeight="1">
+      <x:c r="A11" s="29" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B11" s="29" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E11" s="29"/>
+      <x:c r="F11" s="29"/>
+      <x:c r="G11" s="29"/>
+      <x:c r="H11" s="29" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I11" s="29" t="str">
+        <x:v>2026-07-30 10:00:00</x:v>
+      </x:c>
+      <x:c r="J11" s="29" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b77e5e2502e4b3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,43 +2,46 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Rbec888e06b6f476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R9093d359b9fc4ebd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R797808f789fc4eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R8ccfc2a8f2114a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Radc85e9c1d354474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R0ef10c2b06a74f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rb282f17dbcbd4499"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R6c601ef8560244bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R30bf89e7cdd6478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R28b61dacacc04b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Red65d44f112549ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R63a4332c11ad44e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R6d21670fff6e465b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R32101a24c5484bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="Re41421f691ca4442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="Rff618688102e4a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rf5f5108036f84d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R6e9c2358bd6d441d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Re1926a60086f4a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rfcfc681d596745cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="Rc3764fc9a339426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R110aee2926b34225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R2c20c2a305c24869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R6c06b5c897ed48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="R063507d1793243e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R4f9a118f5e39414a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R622c3eb50daa4192"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R8e5b57b8bbf94145"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R9c9a3efd53884c1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R1b120b9cc3e2412f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R96c733a4a16148e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="Rfdb25040e02c4cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R411834331b1f49cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R15d6b180c4604710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="R2381bbc29a0648be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="Rf7b3fbc2479045dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="Rb0a53faeeae34fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Ra334c737749040ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R24a12bc84a1747a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="Rdf05406df59a4aca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R471bc640d2dd4330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R1a9a9cecaa754ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R48fd18105bd444ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rfa0481eeedf14cb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R3f387f79525a4417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R4db832a1701c46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R649b8c743eae4979"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R2e13f6d218e04584"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Rcfddb9b4295c4b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Ra2fb01499edb47c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R8bfc8392cd13469b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R74f174f402d14039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="R7911fd7419f84817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rf126d999375340a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R7907d5aa6bc64dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Rf48897c49f5542f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rea57ccdba96846a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R9a53809c0a1e421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="Rac0930e3ed7945a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R2380fc1397a54c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="Rd544089d200a409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="Re699f1eea1324ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="Re21eccfbdf6c45f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R188e0dd4b1c542ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R19f44b9cce194602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R52b559c412384c78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="Rc4d9051461e4406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="Rd2bfc726d23148b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="Rb4e2c114ac9346f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R98beb58dc1584f99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="Rda0dda362e244528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="Rbc03d119c78d4d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="R73cb63970ab64ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="R409290cf07ef4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract" sheetId="38" r:id="Rd033fcae38ff488f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract_attachment" sheetId="39" r:id="R30e179abb381422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_scheduled_task_execution" sheetId="40" r:id="R97933aa5b20a4253"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2234,7 +2237,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="28">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -2371,8 +2374,25 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="37">
+  <x:fills count="39">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2554,8 +2574,18 @@
         <x:fgColor rgb="FF5B9BD5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B6A88"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC5E8F4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="14">
+  <x:borders count="16">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -2692,6 +2722,34 @@
       </x:top>
       <x:bottom style="thin">
         <x:color rgb="FFB7B7B7"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9EADB8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9EADB8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9EADB8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9EADB8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF0B6A88"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF0B6A88"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF0B6A88"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF0B6A88"/>
       </x:bottom>
     </x:border>
   </x:borders>
@@ -2845,7 +2903,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
@@ -2920,6 +2978,47 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="37" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="38" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -8040,10 +8139,52 @@
         <x:v>模板阶段内的关键事项和交付要求。</x:v>
       </x:c>
     </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C36" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D36" s="40" t="str">
+        <x:v>产品历次运维合同、续签关系、服务周期和终止信息。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="40" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C37" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="str">
+        <x:v>运维合同附件元数据及 OSS 上传响应。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="40" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C38" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D38" s="40" t="str">
+        <x:v>通用定时任务幂等、执行状态、重试和结果记录。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60f8413ff0d945cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R202202f0e73f46be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26960,6 +27101,1684 @@
       </x:c>
       <x:c r="N407"/>
     </x:row>
+    <x:row r="408" ht="24" hidden="0" customHeight="1">
+      <x:c r="A408" s="40" t="n">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B408" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C408" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D408" s="40" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="E408" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F408" s="40" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G408" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H408" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I408" s="40"/>
+      <x:c r="J408" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K408" s="40" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L408" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M408" s="40" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+      <x:c r="N408" s="40" t="str">
+        <x:v>PRIMARY KEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" ht="60" hidden="0" customHeight="1">
+      <x:c r="A409" s="33" t="n">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B409" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C409" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D409" s="33" t="str">
+        <x:v>产品ID</x:v>
+      </x:c>
+      <x:c r="E409" s="33" t="str">
+        <x:v>product_id</x:v>
+      </x:c>
+      <x:c r="F409" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G409" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H409" s="33"/>
+      <x:c r="I409" s="33" t="str">
+        <x:v>pms_product.id</x:v>
+      </x:c>
+      <x:c r="J409" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K409" s="33"/>
+      <x:c r="L409" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M409" s="33" t="str">
+        <x:v>所属产品。</x:v>
+      </x:c>
+      <x:c r="N409" s="33" t="str">
+        <x:v>NOT NULL, ON DELETE RESTRICT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" ht="48" hidden="0" customHeight="1">
+      <x:c r="A410" s="40" t="n">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B410" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C410" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D410" s="40" t="str">
+        <x:v>上一份合同ID</x:v>
+      </x:c>
+      <x:c r="E410" s="40" t="str">
+        <x:v>previous_contract_id</x:v>
+      </x:c>
+      <x:c r="F410" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G410" s="40"/>
+      <x:c r="H410" s="40" t="str">
+        <x:v>条件唯一</x:v>
+      </x:c>
+      <x:c r="I410" s="40" t="str">
+        <x:v>pms_product_maintenance_contract.id</x:v>
+      </x:c>
+      <x:c r="J410" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K410" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L410" s="40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M410" s="40" t="str">
+        <x:v>续签链中的上一份合同；首份合同为空。</x:v>
+      </x:c>
+      <x:c r="N410" s="40" t="str">
+        <x:v>ON DELETE RESTRICT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" ht="24" hidden="0" customHeight="1">
+      <x:c r="A411" s="33" t="n">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B411" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C411" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D411" s="33" t="str">
+        <x:v>合同编号</x:v>
+      </x:c>
+      <x:c r="E411" s="33" t="str">
+        <x:v>contract_code</x:v>
+      </x:c>
+      <x:c r="F411" s="33" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="G411" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H411" s="33" t="str">
+        <x:v>条件唯一</x:v>
+      </x:c>
+      <x:c r="I411" s="33"/>
+      <x:c r="J411" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K411" s="33"/>
+      <x:c r="L411" s="33" t="str">
+        <x:v>YW-2026-001</x:v>
+      </x:c>
+      <x:c r="M411" s="33" t="str">
+        <x:v>运维合同业务编号。</x:v>
+      </x:c>
+      <x:c r="N411" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" ht="24" hidden="0" customHeight="1">
+      <x:c r="A412" s="40" t="n">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B412" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C412" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D412" s="40" t="str">
+        <x:v>合同名称</x:v>
+      </x:c>
+      <x:c r="E412" s="40" t="str">
+        <x:v>contract_name</x:v>
+      </x:c>
+      <x:c r="F412" s="40" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="G412" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H412" s="40"/>
+      <x:c r="I412" s="40"/>
+      <x:c r="J412" s="40"/>
+      <x:c r="K412" s="40"/>
+      <x:c r="L412" s="40" t="str">
+        <x:v>产品年度运维服务合同</x:v>
+      </x:c>
+      <x:c r="M412" s="40" t="str">
+        <x:v>运维合同名称。</x:v>
+      </x:c>
+      <x:c r="N412" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" ht="60" hidden="0" customHeight="1">
+      <x:c r="A413" s="33" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B413" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C413" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D413" s="33" t="str">
+        <x:v>供应商ID</x:v>
+      </x:c>
+      <x:c r="E413" s="33" t="str">
+        <x:v>supplier_id</x:v>
+      </x:c>
+      <x:c r="F413" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G413" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H413" s="33"/>
+      <x:c r="I413" s="33" t="str">
+        <x:v>pms_archive.id</x:v>
+      </x:c>
+      <x:c r="J413" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K413" s="33"/>
+      <x:c r="L413" s="33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M413" s="33" t="str">
+        <x:v>付款对象，对应供应商档案。</x:v>
+      </x:c>
+      <x:c r="N413" s="33" t="str">
+        <x:v>NOT NULL, ON DELETE RESTRICT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" ht="24" hidden="0" customHeight="1">
+      <x:c r="A414" s="40" t="n">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B414" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C414" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D414" s="40" t="str">
+        <x:v>签订日期</x:v>
+      </x:c>
+      <x:c r="E414" s="40" t="str">
+        <x:v>signed_date</x:v>
+      </x:c>
+      <x:c r="F414" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="G414" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H414" s="40"/>
+      <x:c r="I414" s="40"/>
+      <x:c r="J414" s="40"/>
+      <x:c r="K414" s="40"/>
+      <x:c r="L414" s="40" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="M414" s="40" t="str">
+        <x:v>合同签订日期。</x:v>
+      </x:c>
+      <x:c r="N414" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" ht="24" hidden="0" customHeight="1">
+      <x:c r="A415" s="33" t="n">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B415" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C415" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D415" s="33" t="str">
+        <x:v>服务开始日期</x:v>
+      </x:c>
+      <x:c r="E415" s="33" t="str">
+        <x:v>service_start_date</x:v>
+      </x:c>
+      <x:c r="F415" s="33" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="G415" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H415" s="33"/>
+      <x:c r="I415" s="33"/>
+      <x:c r="J415" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K415" s="33"/>
+      <x:c r="L415" s="33" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="M415" s="33" t="str">
+        <x:v>运维服务开始日期；允许与上一份合同存在空档。</x:v>
+      </x:c>
+      <x:c r="N415" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" ht="24" hidden="0" customHeight="1">
+      <x:c r="A416" s="40" t="n">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B416" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C416" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D416" s="40" t="str">
+        <x:v>服务结束日期</x:v>
+      </x:c>
+      <x:c r="E416" s="40" t="str">
+        <x:v>service_end_date</x:v>
+      </x:c>
+      <x:c r="F416" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="G416" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H416" s="40"/>
+      <x:c r="I416" s="40"/>
+      <x:c r="J416" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K416" s="40"/>
+      <x:c r="L416" s="40" t="str">
+        <x:v>2027-08-31</x:v>
+      </x:c>
+      <x:c r="M416" s="40" t="str">
+        <x:v>运维服务结束日期及固定提醒基准。</x:v>
+      </x:c>
+      <x:c r="N416" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" ht="24" hidden="0" customHeight="1">
+      <x:c r="A417" s="33" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B417" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C417" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D417" s="33" t="str">
+        <x:v>合同金额</x:v>
+      </x:c>
+      <x:c r="E417" s="33" t="str">
+        <x:v>contract_amount</x:v>
+      </x:c>
+      <x:c r="F417" s="33" t="str">
+        <x:v>NUMERIC(18,2)</x:v>
+      </x:c>
+      <x:c r="G417" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H417" s="33"/>
+      <x:c r="I417" s="33"/>
+      <x:c r="J417" s="33"/>
+      <x:c r="K417" s="33"/>
+      <x:c r="L417" s="33" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="M417" s="33" t="str">
+        <x:v>公司应向供应商支付的合同总金额。</x:v>
+      </x:c>
+      <x:c r="N417" s="33" t="str">
+        <x:v>CHECK &gt; 0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" ht="48" hidden="0" customHeight="1">
+      <x:c r="A418" s="40" t="n">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B418" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C418" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D418" s="40" t="str">
+        <x:v>终止日期</x:v>
+      </x:c>
+      <x:c r="E418" s="40" t="str">
+        <x:v>termination_date</x:v>
+      </x:c>
+      <x:c r="F418" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="G418" s="40"/>
+      <x:c r="H418" s="40"/>
+      <x:c r="I418" s="40"/>
+      <x:c r="J418" s="40"/>
+      <x:c r="K418" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L418" s="40" t="str">
+        <x:v>2027-03-31</x:v>
+      </x:c>
+      <x:c r="M418" s="40" t="str">
+        <x:v>提前终止日期，必须位于服务期内。</x:v>
+      </x:c>
+      <x:c r="N418" s="40" t="str">
+        <x:v>与终止原因同时为空或同时填写</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" ht="48" hidden="0" customHeight="1">
+      <x:c r="A419" s="33" t="n">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B419" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C419" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D419" s="33" t="str">
+        <x:v>终止原因</x:v>
+      </x:c>
+      <x:c r="E419" s="33" t="str">
+        <x:v>termination_reason</x:v>
+      </x:c>
+      <x:c r="F419" s="33" t="str">
+        <x:v>VARCHAR(500)</x:v>
+      </x:c>
+      <x:c r="G419" s="33"/>
+      <x:c r="H419" s="33"/>
+      <x:c r="I419" s="33"/>
+      <x:c r="J419" s="33"/>
+      <x:c r="K419" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L419" s="33" t="str">
+        <x:v>供应商违约</x:v>
+      </x:c>
+      <x:c r="M419" s="33" t="str">
+        <x:v>提前终止原因。</x:v>
+      </x:c>
+      <x:c r="N419" s="33" t="str">
+        <x:v>与终止日期同时为空或同时填写</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A420" s="40" t="n">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B420" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C420" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D420" s="40" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+      <x:c r="E420" s="40" t="str">
+        <x:v>remark</x:v>
+      </x:c>
+      <x:c r="F420" s="40" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G420" s="40"/>
+      <x:c r="H420" s="40"/>
+      <x:c r="I420" s="40"/>
+      <x:c r="J420" s="40"/>
+      <x:c r="K420" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L420" s="40" t="str">
+        <x:v>含驻场支持</x:v>
+      </x:c>
+      <x:c r="M420" s="40" t="str">
+        <x:v>业务补充说明。</x:v>
+      </x:c>
+      <x:c r="N420" s="40"/>
+    </x:row>
+    <x:row r="421" ht="48" hidden="0" customHeight="1">
+      <x:c r="A421" s="33" t="n">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B421" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C421" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D421" s="33" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="E421" s="33" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="F421" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G421" s="33"/>
+      <x:c r="H421" s="33"/>
+      <x:c r="I421" s="33" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J421" s="33"/>
+      <x:c r="K421" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L421" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M421" s="33" t="str">
+        <x:v>创建人。</x:v>
+      </x:c>
+      <x:c r="N421" s="33" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" ht="48" hidden="0" customHeight="1">
+      <x:c r="A422" s="40" t="n">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B422" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C422" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D422" s="40" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="E422" s="40" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="F422" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G422" s="40"/>
+      <x:c r="H422" s="40"/>
+      <x:c r="I422" s="40" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J422" s="40"/>
+      <x:c r="K422" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L422" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M422" s="40" t="str">
+        <x:v>最后更新人。</x:v>
+      </x:c>
+      <x:c r="N422" s="40" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" ht="24" hidden="0" customHeight="1">
+      <x:c r="A423" s="33" t="n">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B423" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C423" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D423" s="33" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="E423" s="33" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="F423" s="33" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G423" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H423" s="33"/>
+      <x:c r="I423" s="33"/>
+      <x:c r="J423" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K423" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L423" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M423" s="33" t="str">
+        <x:v>0 正常，1 已删除。</x:v>
+      </x:c>
+      <x:c r="N423" s="33" t="str">
+        <x:v>CHECK IN (0,1)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" ht="24" hidden="0" customHeight="1">
+      <x:c r="A424" s="40" t="n">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B424" s="40" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C424" s="40" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D424" s="40" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E424" s="40" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F424" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G424" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H424" s="40"/>
+      <x:c r="I424" s="40"/>
+      <x:c r="J424" s="40"/>
+      <x:c r="K424" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L424" s="40" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="M424" s="40" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+      <x:c r="N424" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" ht="24" hidden="0" customHeight="1">
+      <x:c r="A425" s="33" t="n">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B425" s="33" t="str">
+        <x:v>pms_product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="C425" s="33" t="str">
+        <x:v>产品运维合同表</x:v>
+      </x:c>
+      <x:c r="D425" s="33" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E425" s="33" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F425" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G425" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H425" s="33"/>
+      <x:c r="I425" s="33"/>
+      <x:c r="J425" s="33"/>
+      <x:c r="K425" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L425" s="33" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="M425" s="33" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N425" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" ht="24" hidden="0" customHeight="1">
+      <x:c r="A426" s="40" t="n">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B426" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C426" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D426" s="40" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="E426" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F426" s="40" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G426" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H426" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I426" s="40"/>
+      <x:c r="J426" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K426" s="40" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L426" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M426" s="40" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+      <x:c r="N426" s="40" t="str">
+        <x:v>PRIMARY KEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" ht="60" hidden="0" customHeight="1">
+      <x:c r="A427" s="33" t="n">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B427" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C427" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D427" s="33" t="str">
+        <x:v>运维合同ID</x:v>
+      </x:c>
+      <x:c r="E427" s="33" t="str">
+        <x:v>contract_id</x:v>
+      </x:c>
+      <x:c r="F427" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G427" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H427" s="33"/>
+      <x:c r="I427" s="33" t="str">
+        <x:v>pms_product_maintenance_contract.id</x:v>
+      </x:c>
+      <x:c r="J427" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K427" s="33"/>
+      <x:c r="L427" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M427" s="33" t="str">
+        <x:v>所属产品运维合同。</x:v>
+      </x:c>
+      <x:c r="N427" s="33" t="str">
+        <x:v>NOT NULL, ON DELETE RESTRICT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" ht="24" hidden="0" customHeight="1">
+      <x:c r="A428" s="40" t="n">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B428" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C428" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D428" s="40" t="str">
+        <x:v>原始文件名</x:v>
+      </x:c>
+      <x:c r="E428" s="40" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="F428" s="40" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="G428" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H428" s="40"/>
+      <x:c r="I428" s="40"/>
+      <x:c r="J428" s="40"/>
+      <x:c r="K428" s="40"/>
+      <x:c r="L428" s="40" t="str">
+        <x:v>运维合同.pdf</x:v>
+      </x:c>
+      <x:c r="M428" s="40" t="str">
+        <x:v>用户上传时的文件名。</x:v>
+      </x:c>
+      <x:c r="N428" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" ht="24" hidden="0" customHeight="1">
+      <x:c r="A429" s="33" t="n">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B429" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C429" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D429" s="33" t="str">
+        <x:v>存储文件名</x:v>
+      </x:c>
+      <x:c r="E429" s="33" t="str">
+        <x:v>storage_name</x:v>
+      </x:c>
+      <x:c r="F429" s="33" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="G429" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H429" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I429" s="33"/>
+      <x:c r="J429" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K429" s="33"/>
+      <x:c r="L429" s="33" t="str">
+        <x:v>contracts/uuid.pdf</x:v>
+      </x:c>
+      <x:c r="M429" s="33" t="str">
+        <x:v>OSS 对象存储名。</x:v>
+      </x:c>
+      <x:c r="N429" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" ht="24" hidden="0" customHeight="1">
+      <x:c r="A430" s="40" t="n">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B430" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C430" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D430" s="40" t="str">
+        <x:v>OSS响应</x:v>
+      </x:c>
+      <x:c r="E430" s="40" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="F430" s="40" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="G430" s="40"/>
+      <x:c r="H430" s="40"/>
+      <x:c r="I430" s="40"/>
+      <x:c r="J430" s="40"/>
+      <x:c r="K430" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L430" s="40" t="str">
+        <x:v>{"url":"..."}</x:v>
+      </x:c>
+      <x:c r="M430" s="40" t="str">
+        <x:v>OSS 上传响应快照。</x:v>
+      </x:c>
+      <x:c r="N430" s="40"/>
+    </x:row>
+    <x:row r="431" ht="24" hidden="0" customHeight="1">
+      <x:c r="A431" s="33" t="n">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B431" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C431" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D431" s="33" t="str">
+        <x:v>MIME类型</x:v>
+      </x:c>
+      <x:c r="E431" s="33" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="F431" s="33" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="G431" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H431" s="33"/>
+      <x:c r="I431" s="33"/>
+      <x:c r="J431" s="33"/>
+      <x:c r="K431" s="33"/>
+      <x:c r="L431" s="33" t="str">
+        <x:v>application/pdf</x:v>
+      </x:c>
+      <x:c r="M431" s="33" t="str">
+        <x:v>附件 MIME 类型。</x:v>
+      </x:c>
+      <x:c r="N431" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" ht="36" hidden="0" customHeight="1">
+      <x:c r="A432" s="40" t="n">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B432" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C432" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D432" s="40" t="str">
+        <x:v>文件大小</x:v>
+      </x:c>
+      <x:c r="E432" s="40" t="str">
+        <x:v>file_size</x:v>
+      </x:c>
+      <x:c r="F432" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G432" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H432" s="40"/>
+      <x:c r="I432" s="40"/>
+      <x:c r="J432" s="40"/>
+      <x:c r="K432" s="40"/>
+      <x:c r="L432" s="40" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+      <x:c r="M432" s="40" t="str">
+        <x:v>附件字节数，最大 20MB。</x:v>
+      </x:c>
+      <x:c r="N432" s="40" t="str">
+        <x:v>CHECK 1..20971520</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" ht="24" hidden="0" customHeight="1">
+      <x:c r="A433" s="33" t="n">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B433" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C433" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D433" s="33" t="str">
+        <x:v>排序值</x:v>
+      </x:c>
+      <x:c r="E433" s="33" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="F433" s="33" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G433" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H433" s="33"/>
+      <x:c r="I433" s="33"/>
+      <x:c r="J433" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K433" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L433" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M433" s="33" t="str">
+        <x:v>附件展示顺序。</x:v>
+      </x:c>
+      <x:c r="N433" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" ht="48" hidden="0" customHeight="1">
+      <x:c r="A434" s="40" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B434" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C434" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D434" s="40" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="E434" s="40" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="F434" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G434" s="40"/>
+      <x:c r="H434" s="40"/>
+      <x:c r="I434" s="40" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J434" s="40"/>
+      <x:c r="K434" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L434" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M434" s="40" t="str">
+        <x:v>创建人。</x:v>
+      </x:c>
+      <x:c r="N434" s="40" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" ht="48" hidden="0" customHeight="1">
+      <x:c r="A435" s="33" t="n">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B435" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C435" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D435" s="33" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="E435" s="33" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="F435" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G435" s="33"/>
+      <x:c r="H435" s="33"/>
+      <x:c r="I435" s="33" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J435" s="33"/>
+      <x:c r="K435" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L435" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M435" s="33" t="str">
+        <x:v>最后更新人。</x:v>
+      </x:c>
+      <x:c r="N435" s="33" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" ht="24" hidden="0" customHeight="1">
+      <x:c r="A436" s="40" t="n">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B436" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C436" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D436" s="40" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="E436" s="40" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="F436" s="40" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G436" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H436" s="40"/>
+      <x:c r="I436" s="40"/>
+      <x:c r="J436" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K436" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L436" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M436" s="40" t="str">
+        <x:v>0 正常，1 已删除。</x:v>
+      </x:c>
+      <x:c r="N436" s="40" t="str">
+        <x:v>CHECK IN (0,1)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" ht="24" hidden="0" customHeight="1">
+      <x:c r="A437" s="33" t="n">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B437" s="33" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C437" s="33" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D437" s="33" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E437" s="33" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F437" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G437" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H437" s="33"/>
+      <x:c r="I437" s="33"/>
+      <x:c r="J437" s="33"/>
+      <x:c r="K437" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L437" s="33" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="M437" s="33" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+      <x:c r="N437" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" ht="24" hidden="0" customHeight="1">
+      <x:c r="A438" s="40" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B438" s="40" t="str">
+        <x:v>pms_product_maintenance_contract_attachment</x:v>
+      </x:c>
+      <x:c r="C438" s="40" t="str">
+        <x:v>产品运维合同附件表</x:v>
+      </x:c>
+      <x:c r="D438" s="40" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E438" s="40" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F438" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G438" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H438" s="40"/>
+      <x:c r="I438" s="40"/>
+      <x:c r="J438" s="40"/>
+      <x:c r="K438" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L438" s="40" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="M438" s="40" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N438" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" ht="24" hidden="0" customHeight="1">
+      <x:c r="A439" s="33" t="n">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B439" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C439" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D439" s="33" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="E439" s="33" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F439" s="33" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G439" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H439" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I439" s="33"/>
+      <x:c r="J439" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K439" s="33" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L439" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M439" s="33" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+      <x:c r="N439" s="33" t="str">
+        <x:v>PRIMARY KEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" ht="24" hidden="0" customHeight="1">
+      <x:c r="A440" s="40" t="n">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B440" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C440" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D440" s="40" t="str">
+        <x:v>任务编码</x:v>
+      </x:c>
+      <x:c r="E440" s="40" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+      <x:c r="F440" s="40" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="G440" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H440" s="40" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="I440" s="40"/>
+      <x:c r="J440" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K440" s="40"/>
+      <x:c r="L440" s="40" t="str">
+        <x:v>product_maintenance_contract_reminder</x:v>
+      </x:c>
+      <x:c r="M440" s="40" t="str">
+        <x:v>定时任务稳定编码。</x:v>
+      </x:c>
+      <x:c r="N440" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" ht="24" hidden="0" customHeight="1">
+      <x:c r="A441" s="33" t="n">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B441" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C441" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D441" s="33" t="str">
+        <x:v>目标类型</x:v>
+      </x:c>
+      <x:c r="E441" s="33" t="str">
+        <x:v>target_type</x:v>
+      </x:c>
+      <x:c r="F441" s="33" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="G441" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H441" s="33" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="I441" s="33"/>
+      <x:c r="J441" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K441" s="33"/>
+      <x:c r="L441" s="33" t="str">
+        <x:v>product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="M441" s="33" t="str">
+        <x:v>业务目标类型。</x:v>
+      </x:c>
+      <x:c r="N441" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" ht="24" hidden="0" customHeight="1">
+      <x:c r="A442" s="40" t="n">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B442" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C442" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D442" s="40" t="str">
+        <x:v>目标ID</x:v>
+      </x:c>
+      <x:c r="E442" s="40" t="str">
+        <x:v>target_id</x:v>
+      </x:c>
+      <x:c r="F442" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G442" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H442" s="40" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="I442" s="40"/>
+      <x:c r="J442" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K442" s="40"/>
+      <x:c r="L442" s="40" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M442" s="40" t="str">
+        <x:v>业务目标主键。</x:v>
+      </x:c>
+      <x:c r="N442" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" ht="24" hidden="0" customHeight="1">
+      <x:c r="A443" s="33" t="n">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B443" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C443" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D443" s="33" t="str">
+        <x:v>执行键</x:v>
+      </x:c>
+      <x:c r="E443" s="33" t="str">
+        <x:v>execution_key</x:v>
+      </x:c>
+      <x:c r="F443" s="33" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="G443" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H443" s="33" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="I443" s="33"/>
+      <x:c r="J443" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K443" s="33"/>
+      <x:c r="L443" s="33" t="str">
+        <x:v>before:30:2027-08-31</x:v>
+      </x:c>
+      <x:c r="M443" s="33" t="str">
+        <x:v>同一目标内的幂等触发节点。</x:v>
+      </x:c>
+      <x:c r="N443" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A444" s="40" t="n">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B444" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C444" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D444" s="40" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="E444" s="40" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="F444" s="40" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="G444" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H444" s="40"/>
+      <x:c r="I444" s="40"/>
+      <x:c r="J444" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K444" s="40"/>
+      <x:c r="L444" s="40" t="str">
+        <x:v>success</x:v>
+      </x:c>
+      <x:c r="M444" s="40" t="str">
+        <x:v>running、success 或 failed。</x:v>
+      </x:c>
+      <x:c r="N444" s="40" t="str">
+        <x:v>CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" ht="24" hidden="0" customHeight="1">
+      <x:c r="A445" s="33" t="n">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B445" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C445" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D445" s="33" t="str">
+        <x:v>尝试次数</x:v>
+      </x:c>
+      <x:c r="E445" s="33" t="str">
+        <x:v>attempt_count</x:v>
+      </x:c>
+      <x:c r="F445" s="33" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G445" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H445" s="33"/>
+      <x:c r="I445" s="33"/>
+      <x:c r="J445" s="33"/>
+      <x:c r="K445" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L445" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M445" s="33" t="str">
+        <x:v>失败重试累计次数。</x:v>
+      </x:c>
+      <x:c r="N445" s="33" t="str">
+        <x:v>CHECK &gt; 0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A446" s="40" t="n">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B446" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C446" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D446" s="40" t="str">
+        <x:v>错误信息</x:v>
+      </x:c>
+      <x:c r="E446" s="40" t="str">
+        <x:v>error_message</x:v>
+      </x:c>
+      <x:c r="F446" s="40" t="str">
+        <x:v>VARCHAR(500)</x:v>
+      </x:c>
+      <x:c r="G446" s="40"/>
+      <x:c r="H446" s="40"/>
+      <x:c r="I446" s="40"/>
+      <x:c r="J446" s="40"/>
+      <x:c r="K446" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L446" s="40" t="str">
+        <x:v>消息写入失败</x:v>
+      </x:c>
+      <x:c r="M446" s="40" t="str">
+        <x:v>最近一次失败信息。</x:v>
+      </x:c>
+      <x:c r="N446" s="40"/>
+    </x:row>
+    <x:row r="447" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A447" s="33" t="n">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B447" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C447" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D447" s="33" t="str">
+        <x:v>结果数据</x:v>
+      </x:c>
+      <x:c r="E447" s="33" t="str">
+        <x:v>result_data</x:v>
+      </x:c>
+      <x:c r="F447" s="33" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="G447" s="33"/>
+      <x:c r="H447" s="33"/>
+      <x:c r="I447" s="33"/>
+      <x:c r="J447" s="33"/>
+      <x:c r="K447" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L447" s="33" t="str">
+        <x:v>{"messageId":10}</x:v>
+      </x:c>
+      <x:c r="M447" s="33" t="str">
+        <x:v>成功执行后的结构化结果。</x:v>
+      </x:c>
+      <x:c r="N447" s="33"/>
+    </x:row>
+    <x:row r="448" ht="24" hidden="0" customHeight="1">
+      <x:c r="A448" s="40" t="n">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B448" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C448" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D448" s="40" t="str">
+        <x:v>开始时间</x:v>
+      </x:c>
+      <x:c r="E448" s="40" t="str">
+        <x:v>started_at</x:v>
+      </x:c>
+      <x:c r="F448" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G448" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H448" s="40"/>
+      <x:c r="I448" s="40"/>
+      <x:c r="J448" s="40"/>
+      <x:c r="K448" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L448" s="40" t="str">
+        <x:v>2026-08-04 08:30:00</x:v>
+      </x:c>
+      <x:c r="M448" s="40" t="str">
+        <x:v>最近一次执行开始时间。</x:v>
+      </x:c>
+      <x:c r="N448" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" ht="16.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A449" s="33" t="n">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B449" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C449" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D449" s="33" t="str">
+        <x:v>完成时间</x:v>
+      </x:c>
+      <x:c r="E449" s="33" t="str">
+        <x:v>finished_at</x:v>
+      </x:c>
+      <x:c r="F449" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G449" s="33"/>
+      <x:c r="H449" s="33"/>
+      <x:c r="I449" s="33"/>
+      <x:c r="J449" s="33"/>
+      <x:c r="K449" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L449" s="33" t="str">
+        <x:v>2026-08-04 08:30:01</x:v>
+      </x:c>
+      <x:c r="M449" s="33" t="str">
+        <x:v>最近一次执行完成时间。</x:v>
+      </x:c>
+      <x:c r="N449" s="33"/>
+    </x:row>
+    <x:row r="450" ht="24" hidden="0" customHeight="1">
+      <x:c r="A450" s="40" t="n">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B450" s="40" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C450" s="40" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D450" s="40" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E450" s="40" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F450" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G450" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H450" s="40"/>
+      <x:c r="I450" s="40"/>
+      <x:c r="J450" s="40"/>
+      <x:c r="K450" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L450" s="40" t="str">
+        <x:v>2026-08-04 08:30:00</x:v>
+      </x:c>
+      <x:c r="M450" s="40" t="str">
+        <x:v>首次创建时间。</x:v>
+      </x:c>
+      <x:c r="N450" s="40" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" ht="24" hidden="0" customHeight="1">
+      <x:c r="A451" s="33" t="n">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B451" s="33" t="str">
+        <x:v>pms_scheduled_task_execution</x:v>
+      </x:c>
+      <x:c r="C451" s="33" t="str">
+        <x:v>定时任务执行表</x:v>
+      </x:c>
+      <x:c r="D451" s="33" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E451" s="33" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F451" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G451" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H451" s="33"/>
+      <x:c r="I451" s="33"/>
+      <x:c r="J451" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K451" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L451" s="33" t="str">
+        <x:v>2026-08-04 08:30:01</x:v>
+      </x:c>
+      <x:c r="M451" s="33" t="str">
+        <x:v>最后状态更新时间。</x:v>
+      </x:c>
+      <x:c r="N451" s="33" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
@@ -26967,7 +28786,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R594081a923d54890"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R084f4af7ceac4a29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28020,7 +29839,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9729e2913c604d0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d483fafacf4591"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28599,7 +30418,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf770be862a5f43d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0658cb8308c944af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29010,7 +30829,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f10298c546e414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669ab833485d447d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29297,7 +31116,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e2ecb461e304e08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c95d80f157e4959"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29558,7 +31377,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10cf648a2533420d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read8bbed9cfe4084"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29871,8 +31690,962 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b77e5e2502e4b3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R975fd239b14c4e0d"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>pms_product_maintenance_contract（产品运维合同表）</x:v>
+      </x:c>
+      <x:c r="B1" s="35"/>
+      <x:c r="C1" s="35"/>
+      <x:c r="D1" s="35"/>
+      <x:c r="E1" s="35"/>
+      <x:c r="F1" s="35"/>
+      <x:c r="G1" s="35"/>
+      <x:c r="H1" s="35"/>
+      <x:c r="I1" s="35"/>
+      <x:c r="J1" s="35"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="39" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="B3" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="40" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="40"/>
+      <x:c r="G3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="40" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="40" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="33" t="str">
+        <x:v>产品ID</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>product_id</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="33"/>
+      <x:c r="F4" s="33" t="str">
+        <x:v>pms_product.id</x:v>
+      </x:c>
+      <x:c r="G4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="33"/>
+      <x:c r="I4" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J4" s="33" t="str">
+        <x:v>所属产品。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="24" hidden="0" customHeight="1">
+      <x:c r="A5" s="40" t="str">
+        <x:v>上一份合同ID</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>previous_contract_id</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D5" s="40"/>
+      <x:c r="E5" s="40" t="str">
+        <x:v>条件唯一</x:v>
+      </x:c>
+      <x:c r="F5" s="40" t="str">
+        <x:v>pms_product_maintenance_contract.id</x:v>
+      </x:c>
+      <x:c r="G5" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H5" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I5" s="40" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J5" s="40" t="str">
+        <x:v>续签链中的上一份合同；首份合同为空。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="33" t="str">
+        <x:v>合同编号</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>contract_code</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="str">
+        <x:v>条件唯一</x:v>
+      </x:c>
+      <x:c r="F6" s="33"/>
+      <x:c r="G6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H6" s="33"/>
+      <x:c r="I6" s="33" t="str">
+        <x:v>YW-2026-001</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="str">
+        <x:v>运维合同业务编号。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>合同名称</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:v>contract_name</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="D7" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="40" t="str">
+        <x:v>产品年度运维服务合同</x:v>
+      </x:c>
+      <x:c r="J7" s="40" t="str">
+        <x:v>运维合同名称。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="33" t="str">
+        <x:v>供应商ID</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>supplier_id</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="33"/>
+      <x:c r="F8" s="33" t="str">
+        <x:v>pms_archive.id</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H8" s="33"/>
+      <x:c r="I8" s="33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="str">
+        <x:v>付款对象，对应供应商档案。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="40" t="str">
+        <x:v>签订日期</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:v>signed_date</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="40" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="J9" s="40" t="str">
+        <x:v>合同签订日期。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="33" t="str">
+        <x:v>服务开始日期</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>service_start_date</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H10" s="33"/>
+      <x:c r="I10" s="33" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="J10" s="33" t="str">
+        <x:v>运维服务开始日期；允许与上一份合同存在空档。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="40" t="str">
+        <x:v>服务结束日期</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>service_end_date</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H11" s="40"/>
+      <x:c r="I11" s="40" t="str">
+        <x:v>2027-08-31</x:v>
+      </x:c>
+      <x:c r="J11" s="40" t="str">
+        <x:v>运维服务结束日期及固定提醒基准。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="33" t="str">
+        <x:v>合同金额</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>contract_amount</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="str">
+        <x:v>NUMERIC(18,2)</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E12" s="33"/>
+      <x:c r="F12" s="33"/>
+      <x:c r="G12" s="33"/>
+      <x:c r="H12" s="33"/>
+      <x:c r="I12" s="33" t="n">
+        <x:v>120000</x:v>
+      </x:c>
+      <x:c r="J12" s="33" t="str">
+        <x:v>公司应向供应商支付的合同总金额。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="40" t="str">
+        <x:v>终止日期</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:v>termination_date</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:v>DATE</x:v>
+      </x:c>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I13" s="40" t="str">
+        <x:v>2027-03-31</x:v>
+      </x:c>
+      <x:c r="J13" s="40" t="str">
+        <x:v>提前终止日期，必须位于服务期内。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="33" t="str">
+        <x:v>终止原因</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>termination_reason</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="str">
+        <x:v>VARCHAR(500)</x:v>
+      </x:c>
+      <x:c r="D14" s="33"/>
+      <x:c r="E14" s="33"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14" s="33"/>
+      <x:c r="H14" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I14" s="33" t="str">
+        <x:v>供应商违约</x:v>
+      </x:c>
+      <x:c r="J14" s="33" t="str">
+        <x:v>提前终止原因。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="40" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>remark</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="str">
+        <x:v>含驻场支持</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="str">
+        <x:v>业务补充说明。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="33" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D16" s="33"/>
+      <x:c r="E16" s="33"/>
+      <x:c r="F16" s="33" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G16" s="33"/>
+      <x:c r="H16" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I16" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="33" t="str">
+        <x:v>创建人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="40" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D17" s="40"/>
+      <x:c r="E17" s="40"/>
+      <x:c r="F17" s="40" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G17" s="40"/>
+      <x:c r="H17" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I17" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="40" t="str">
+        <x:v>最后更新人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="33" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="B18" s="33" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="C18" s="33" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D18" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E18" s="33"/>
+      <x:c r="F18" s="33"/>
+      <x:c r="G18" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H18" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="33" t="str">
+        <x:v>0 正常，1 已删除。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="40" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B19" s="40" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C19" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D19" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E19" s="40"/>
+      <x:c r="F19" s="40"/>
+      <x:c r="G19" s="40"/>
+      <x:c r="H19" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I19" s="40" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="J19" s="40" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="33" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B20" s="33" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C20" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D20" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E20" s="33"/>
+      <x:c r="F20" s="33"/>
+      <x:c r="G20" s="33"/>
+      <x:c r="H20" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I20" s="33" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="J20" s="33" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>pms_product_maintenance_contract_attachment（产品运维合同附件表）</x:v>
+      </x:c>
+      <x:c r="B1" s="35"/>
+      <x:c r="C1" s="35"/>
+      <x:c r="D1" s="35"/>
+      <x:c r="E1" s="35"/>
+      <x:c r="F1" s="35"/>
+      <x:c r="G1" s="35"/>
+      <x:c r="H1" s="35"/>
+      <x:c r="I1" s="35"/>
+      <x:c r="J1" s="35"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="39" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="B3" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="40" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="40"/>
+      <x:c r="G3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="40" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="40" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" hidden="0" customHeight="1">
+      <x:c r="A4" s="33" t="str">
+        <x:v>运维合同ID</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>contract_id</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="33"/>
+      <x:c r="F4" s="33" t="str">
+        <x:v>pms_product_maintenance_contract.id</x:v>
+      </x:c>
+      <x:c r="G4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="33"/>
+      <x:c r="I4" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J4" s="33" t="str">
+        <x:v>所属产品运维合同。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="40" t="str">
+        <x:v>原始文件名</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="40"/>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40"/>
+      <x:c r="H5" s="40"/>
+      <x:c r="I5" s="40" t="str">
+        <x:v>运维合同.pdf</x:v>
+      </x:c>
+      <x:c r="J5" s="40" t="str">
+        <x:v>用户上传时的文件名。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="33" t="str">
+        <x:v>存储文件名</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>storage_name</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F6" s="33"/>
+      <x:c r="G6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H6" s="33"/>
+      <x:c r="I6" s="33" t="str">
+        <x:v>contracts/uuid.pdf</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="str">
+        <x:v>OSS 对象存储名。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>OSS响应</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I7" s="40" t="str">
+        <x:v>{"url":"..."}</x:v>
+      </x:c>
+      <x:c r="J7" s="40" t="str">
+        <x:v>OSS 上传响应快照。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="33" t="str">
+        <x:v>MIME类型</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="33"/>
+      <x:c r="F8" s="33"/>
+      <x:c r="G8" s="33"/>
+      <x:c r="H8" s="33"/>
+      <x:c r="I8" s="33" t="str">
+        <x:v>application/pdf</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="str">
+        <x:v>附件 MIME 类型。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="40" t="str">
+        <x:v>文件大小</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:v>file_size</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="40" t="n">
+        <x:v>102400</x:v>
+      </x:c>
+      <x:c r="J9" s="40" t="str">
+        <x:v>附件字节数，最大 20MB。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="33" t="str">
+        <x:v>排序值</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H10" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="33" t="str">
+        <x:v>附件展示顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="40" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I11" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="40" t="str">
+        <x:v>创建人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="33" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D12" s="33"/>
+      <x:c r="E12" s="33"/>
+      <x:c r="F12" s="33" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G12" s="33"/>
+      <x:c r="H12" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I12" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="33" t="str">
+        <x:v>最后更新人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="40" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J13" s="40" t="str">
+        <x:v>0 正常，1 已删除。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="33" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E14" s="33"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14" s="33"/>
+      <x:c r="H14" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I14" s="33" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="J14" s="33" t="str">
+        <x:v>记录创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="40" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="str">
+        <x:v>2026-08-04 10:00:00</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -30281,6 +33054,422 @@
       </x:c>
       <x:c r="J15" s="5" t="s">
         <x:v>192</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="44" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>pms_scheduled_task_execution（定时任务执行表）</x:v>
+      </x:c>
+      <x:c r="B1" s="35"/>
+      <x:c r="C1" s="35"/>
+      <x:c r="D1" s="35"/>
+      <x:c r="E1" s="35"/>
+      <x:c r="F1" s="35"/>
+      <x:c r="G1" s="35"/>
+      <x:c r="H1" s="35"/>
+      <x:c r="I1" s="35"/>
+      <x:c r="J1" s="35"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="39" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="39" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="39" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="39" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="39" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="39" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="39" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="40" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="B3" s="40" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="40" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="40"/>
+      <x:c r="G3" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="40" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="40" t="str">
+        <x:v>数据库主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" hidden="0" customHeight="1">
+      <x:c r="A4" s="33" t="str">
+        <x:v>任务编码</x:v>
+      </x:c>
+      <x:c r="B4" s="33" t="str">
+        <x:v>task_code</x:v>
+      </x:c>
+      <x:c r="C4" s="33" t="str">
+        <x:v>VARCHAR(100)</x:v>
+      </x:c>
+      <x:c r="D4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="33" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="F4" s="33"/>
+      <x:c r="G4" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="33"/>
+      <x:c r="I4" s="33" t="str">
+        <x:v>product_maintenance_contract_reminder</x:v>
+      </x:c>
+      <x:c r="J4" s="33" t="str">
+        <x:v>定时任务稳定编码。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="40" t="str">
+        <x:v>目标类型</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:v>target_type</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:v>VARCHAR(50)</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="40" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H5" s="40"/>
+      <x:c r="I5" s="40" t="str">
+        <x:v>product_maintenance_contract</x:v>
+      </x:c>
+      <x:c r="J5" s="40" t="str">
+        <x:v>业务目标类型。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="33" t="str">
+        <x:v>目标ID</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="str">
+        <x:v>target_id</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="F6" s="33"/>
+      <x:c r="G6" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H6" s="33"/>
+      <x:c r="I6" s="33" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J6" s="33" t="str">
+        <x:v>业务目标主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="40" t="str">
+        <x:v>执行键</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:v>execution_key</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="D7" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E7" s="40" t="str">
+        <x:v>组合唯一</x:v>
+      </x:c>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="40" t="str">
+        <x:v>before:30:2027-08-31</x:v>
+      </x:c>
+      <x:c r="J7" s="40" t="str">
+        <x:v>同一目标内的幂等触发节点。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="33" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="B8" s="33" t="str">
+        <x:v>status</x:v>
+      </x:c>
+      <x:c r="C8" s="33" t="str">
+        <x:v>VARCHAR(20)</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="33"/>
+      <x:c r="F8" s="33"/>
+      <x:c r="G8" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H8" s="33"/>
+      <x:c r="I8" s="33" t="str">
+        <x:v>success</x:v>
+      </x:c>
+      <x:c r="J8" s="33" t="str">
+        <x:v>running、success 或 failed。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="40" t="str">
+        <x:v>尝试次数</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:v>attempt_count</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="40" t="str">
+        <x:v>失败重试累计次数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="33" t="str">
+        <x:v>错误信息</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>error_message</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="str">
+        <x:v>VARCHAR(500)</x:v>
+      </x:c>
+      <x:c r="D10" s="33"/>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10" s="33"/>
+      <x:c r="H10" s="33" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I10" s="33" t="str">
+        <x:v>消息写入失败</x:v>
+      </x:c>
+      <x:c r="J10" s="33" t="str">
+        <x:v>最近一次失败信息。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="40" t="str">
+        <x:v>结果数据</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:v>result_data</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I11" s="40" t="str">
+        <x:v>{"messageId":10}</x:v>
+      </x:c>
+      <x:c r="J11" s="40" t="str">
+        <x:v>成功执行后的结构化结果。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="33" t="str">
+        <x:v>开始时间</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>started_at</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E12" s="33"/>
+      <x:c r="F12" s="33"/>
+      <x:c r="G12" s="33"/>
+      <x:c r="H12" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I12" s="33" t="str">
+        <x:v>2026-08-04 08:30:00</x:v>
+      </x:c>
+      <x:c r="J12" s="33" t="str">
+        <x:v>最近一次执行开始时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="40" t="str">
+        <x:v>完成时间</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:v>finished_at</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I13" s="40" t="str">
+        <x:v>2026-08-04 08:30:01</x:v>
+      </x:c>
+      <x:c r="J13" s="40" t="str">
+        <x:v>最近一次执行完成时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="33" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E14" s="33"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14" s="33"/>
+      <x:c r="H14" s="33" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I14" s="33" t="str">
+        <x:v>2026-08-04 08:30:00</x:v>
+      </x:c>
+      <x:c r="J14" s="33" t="str">
+        <x:v>首次创建时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="40" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H15" s="40" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I15" s="40" t="str">
+        <x:v>2026-08-04 08:30:01</x:v>
+      </x:c>
+      <x:c r="J15" s="40" t="str">
+        <x:v>最后状态更新时间。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,46 +2,46 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="Ra334c737749040ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R24a12bc84a1747a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="Rdf05406df59a4aca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R471bc640d2dd4330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R1a9a9cecaa754ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R48fd18105bd444ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rfa0481eeedf14cb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R3f387f79525a4417"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R4db832a1701c46b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R649b8c743eae4979"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R2e13f6d218e04584"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="Rcfddb9b4295c4b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Ra2fb01499edb47c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R8bfc8392cd13469b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R74f174f402d14039"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="R7911fd7419f84817"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rf126d999375340a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R7907d5aa6bc64dfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Rf48897c49f5542f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rea57ccdba96846a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R9a53809c0a1e421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="Rac0930e3ed7945a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R2380fc1397a54c96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="Rd544089d200a409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="Re699f1eea1324ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="Re21eccfbdf6c45f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R188e0dd4b1c542ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R19f44b9cce194602"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R52b559c412384c78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="Rc4d9051461e4406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="Rd2bfc726d23148b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="Rb4e2c114ac9346f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R98beb58dc1584f99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="Rda0dda362e244528"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="Rbc03d119c78d4d7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="R73cb63970ab64ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="R409290cf07ef4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract" sheetId="38" r:id="Rd033fcae38ff488f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract_attachment" sheetId="39" r:id="R30e179abb381422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_scheduled_task_execution" sheetId="40" r:id="R97933aa5b20a4253"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R5b83d41ecaef430a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Rbd42653adca64064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="R4af95da8eab54a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R0f26a406bc784fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="R7d1dcb8e3edd491b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R031496f950dd4f9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="Rf6cb100cf1784622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R32b7760b3f6a449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R1f758757b95044b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R8f5cb85f60a043cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R42b901ce47754ed6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R4178fb0a26db48f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R7b43fb91c17f4325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R71640a0c238044b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R69e7c3144a7044e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="R88221efa487445e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="R5df2583a54ce4447"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="Rfda5f84be30041ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="Ra612779537464c4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="R4036c6acfec24122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="Rb4b58e7e1163447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R37b05ccdd6c24cf7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="Re72de7dab1994225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R42bfbfe5a8914544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="Rf79227c3068f4edc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="R5c5d8108c49b4b34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="Rbc35d7191fc64434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R228549502044487e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R9f4544cdad1843ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="Rf4f5464f2c4f4721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R7e012fb0967446c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="R04299aac30d149f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="Rf0d1bb1d873348dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R7b0aeaafac4f4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="R0257e3191dda4cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="R892a1e98aa534022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="Re7a3ef79dbe04749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract" sheetId="38" r:id="R9baf5338ac564e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract_attachment" sheetId="39" r:id="R29ec3ac7f0a04dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_scheduled_task_execution" sheetId="40" r:id="R1d1e02f12fae432c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1606,448 +1606,448 @@
     <x:t xml:space="preserve">所属产品</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">负责人</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">优先级</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">priority</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">当前状态</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">逾期状态</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">提出日期</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">submit_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pause_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">完成情况</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">completion_status</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">创建人</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">更新人</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">软删除标记</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_task（任务表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">任务编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">任务名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">任务描述</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">所属主任务ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">parent_task_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_task.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">所属主任务；为空表示主任务</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">source_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联项目</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联需求</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">requirement_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_requirement.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_task_owner（任务负责人关联表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">任务ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">task_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">组合唯一</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">任务</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">平级负责人</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">负责人展示顺序</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_bug（BUG表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BUG编号</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bug标题</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bug描述（富文本）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BUG类型ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bug_type_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Bug类型（基础档案）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">严重程度</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">severity</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">严重程度：低、中、高、致命</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0 新建，1 已修复，2 已关闭，3 被激活</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">指派人ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">assignee_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">指派给</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">解决方案ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">resolution_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">解决方案（基础档案）；被激活时保留，再次修复时更新</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">修复时间；被激活时保留，再次修复时更新</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">resolved_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关闭时间</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">closed_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">最近一次激活原因；修复或关闭后保留，再次激活时更新</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_contract（项目合同表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同主键。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">所属项目ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联项目；一个项目最多一份未删除合同。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同编码</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">contract_code</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HT-2026-001</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同编码；未删除数据唯一。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">contract_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">系统建设服务合同</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同名称。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">供应商ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">supplier_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联供应商基础档案；合同引用期间限制删除。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">签订时间</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">signed_date</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同签订日期。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同金额</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">contract_amount</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">NUMERIC(18,2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同金额，必须大于 0；已付和未付金额实时汇总。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">备注</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">remark</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">项目合同补充说明</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">合同备注，可不填写。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-07-20 10:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_payment_stage（项目付款阶段表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款阶段主键。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">所属合同ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">contract_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_contract.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联项目合同。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">阶段</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">stage_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">验收款</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">同一合同内未删除阶段名称唯一。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">计划金额</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">planned_amount</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">阶段计划金额，必须大于 0。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款阶段显示顺序。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_payment_record（项目付款记录表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款记录主键。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款阶段ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">stage_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_payment_stage.id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联付款阶段。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">本次付款金额</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">payment_amount</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">本次付款金额，必须大于 0 且不超过阶段待付金额。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款时间</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">payment_month</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-07-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">页面选择到月，数据库统一保存为所选月份第一天。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">经办人ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">handler_id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">实际付款经办人。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">首笔验收款</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款备注。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款登记人。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">付款登记时间。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_contract_attachment（项目合同附件表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">附件主键。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">关联合同；合同删除时限制删除。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">原文件名</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">original_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">项目合同.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">上传时的原文件名。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">存储文件名</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">storage_name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">20260724/合同文件.pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OSS 文件路径；历史数据为服务端随机存储名。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OSS响应</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">oss_response</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">JSONB</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">{"code":100,"msg":"success","data":[...]}</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">OSS 上传接口返回的完整 JSON；历史本地附件为空。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">文件类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">mime_type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VARCHAR(150)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">application/pdf</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">文件 MIME 类型。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">文件大小</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">file_size</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">单位字节；大于0且不超过20971520。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">同一合同附件的显示顺序。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">记录上传人。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-07-21 10:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">记录上传时间。</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pms_project_plan_stage（项目计划阶段表）</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">阶段 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">所属项目</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">负责人</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">优先级</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">priority</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">当前状态</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">逾期状态</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">提出日期</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">submit_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pause_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">完成情况</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">completion_status</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">创建人</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">更新人</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">软删除标记</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_task（任务表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">任务编号</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">任务名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">任务描述</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">所属主任务ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">parent_task_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_task.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">所属主任务；为空表示主任务</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">source_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联项目</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联需求</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">requirement_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_requirement.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_task_owner（任务负责人关联表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">任务ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">task_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">组合唯一</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">任务</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">平级负责人</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">负责人展示顺序</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_bug（BUG表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BUG编号</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bug标题</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bug描述（富文本）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BUG类型ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bug_type_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bug类型（基础档案）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">严重程度</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">severity</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">严重程度：低、中、高、致命</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0 新建，1 已修复，2 已关闭，3 被激活</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">指派人ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">assignee_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">指派给</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">解决方案ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">resolution_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">解决方案（基础档案）；被激活时保留，再次修复时更新</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">修复时间；被激活时保留，再次修复时更新</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">resolved_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关闭时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">closed_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">最近一次激活原因；修复或关闭后保留，再次激活时更新</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_contract（项目合同表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同主键。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">所属项目ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联项目；一个项目最多一份未删除合同。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同编码</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">contract_code</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HT-2026-001</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同编码；未删除数据唯一。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">contract_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">系统建设服务合同</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同名称。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">供应商ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">supplier_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联供应商基础档案；合同引用期间限制删除。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">签订时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">signed_date</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同签订日期。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同金额</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">contract_amount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NUMERIC(18,2)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同金额，必须大于 0；已付和未付金额实时汇总。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">备注</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">remark</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">项目合同补充说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合同备注，可不填写。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026-07-20 10:00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_payment_stage（项目付款阶段表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款阶段主键。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">所属合同ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">contract_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_contract.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联项目合同。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">阶段</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">stage_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">验收款</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">同一合同内未删除阶段名称唯一。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">计划金额</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">planned_amount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">阶段计划金额，必须大于 0。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款阶段显示顺序。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_payment_record（项目付款记录表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款记录主键。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款阶段ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">stage_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_payment_stage.id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联付款阶段。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">本次付款金额</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">payment_amount</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">本次付款金额，必须大于 0 且不超过阶段待付金额。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">payment_month</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026-07-01</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">页面选择到月，数据库统一保存为所选月份第一天。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">经办人ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">handler_id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">实际付款经办人。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">首笔验收款</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款备注。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款登记人。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">付款登记时间。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_contract_attachment（项目合同附件表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">附件主键。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">关联合同；合同删除时限制删除。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">原文件名</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">original_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">项目合同.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">上传时的原文件名。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">存储文件名</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">storage_name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">20260724/合同文件.pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OSS 文件路径；历史数据为服务端随机存储名。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OSS响应</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">oss_response</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">JSONB</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">{"code":100,"msg":"success","data":[...]}</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OSS 上传接口返回的完整 JSON；历史本地附件为空。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">文件类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mime_type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VARCHAR(150)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">application/pdf</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">文件 MIME 类型。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">文件大小</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">file_size</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">单位字节；大于0且不超过20971520。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">同一合同附件的显示顺序。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">记录上传人。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026-07-21 10:00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">记录上传时间。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pms_project_plan_stage（项目计划阶段表）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">阶段 ID</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">阶段名称</x:t>
@@ -6489,67 +6489,71 @@
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
-      <x:c r="A7" s="5" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="E7" s="6"/>
-      <x:c r="F7" s="5" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5">
+      <x:c r="A7" s="5" t="str">
+        <x:v>所属需求ID</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>requirement_id</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>历史数据可空</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>有效项目唯一</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="str">
+        <x:v>pms_requirement.id</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="5" t="s">
-        <x:v>477</x:v>
+      <x:c r="J7" s="5" t="str">
+        <x:v>所属需求；新建和编辑项目时必填。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E8" s="6"/>
-      <x:c r="F8" s="5"/>
+      <x:c r="F8" s="5" t="s">
+        <x:v>170</x:v>
+      </x:c>
       <x:c r="G8" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H8" s="5" t="s">
-        <x:v>178</x:v>
-      </x:c>
+      <x:c r="H8" s="5"/>
       <x:c r="I8" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
-        <x:v>478</x:v>
+        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>479</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>277</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>161</x:v>
@@ -6569,89 +6573,93 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="5" t="s">
-        <x:v>278</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>480</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>481</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
-        <x:v>482</x:v>
-      </x:c>
-      <x:c r="D10" s="6"/>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E10" s="6"/>
       <x:c r="F10" s="5"/>
-      <x:c r="G10" s="6"/>
+      <x:c r="G10" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="H10" s="5" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="s">
-        <x:v>483</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="I10" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>484</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>485</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>486</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
       <x:c r="F11" s="5"/>
-      <x:c r="G11" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H11" s="5"/>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="5" t="s">
+        <x:v>171</x:v>
+      </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="J11" s="5" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="12" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>490</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="D12" s="6"/>
+      <x:c r="D12" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="5"/>
-      <x:c r="G12" s="6"/>
-      <x:c r="H12" s="5" t="s">
-        <x:v>171</x:v>
-      </x:c>
+      <x:c r="G12" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H12" s="5"/>
       <x:c r="I12" s="5" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>492</x:v>
+        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="13" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>493</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>289</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
         <x:v>482</x:v>
@@ -6664,21 +6672,21 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>494</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="J13" s="5" t="s">
-        <x:v>495</x:v>
+        <x:v>492</x:v>
       </x:c>
     </x:row>
     <x:row r="14" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>496</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>497</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>261</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="D14" s="6"/>
       <x:c r="E14" s="6"/>
@@ -6688,18 +6696,18 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>498</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
-        <x:v>499</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>501</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
         <x:v>261</x:v>
@@ -6712,44 +6720,42 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>502</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="J15" s="5" t="s">
-        <x:v>503</x:v>
+        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="16" customHeight="1">
       <x:c r="A16" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D16" s="6"/>
       <x:c r="E16" s="6"/>
-      <x:c r="F16" s="5" t="s">
-        <x:v>170</x:v>
-      </x:c>
+      <x:c r="F16" s="5"/>
       <x:c r="G16" s="6"/>
       <x:c r="H16" s="5" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="I16" s="5">
-        <x:v>1</x:v>
+      <x:c r="I16" s="5" t="s">
+        <x:v>502</x:v>
       </x:c>
       <x:c r="J16" s="5" t="s">
-        <x:v>172</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
     <x:row r="17" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>173</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
         <x:v>169</x:v>
@@ -6767,69 +6773,69 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J17" s="5" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="18" customHeight="1">
       <x:c r="A18" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D18" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="D18" s="6"/>
       <x:c r="E18" s="6"/>
-      <x:c r="F18" s="5"/>
-      <x:c r="G18" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="F18" s="5" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G18" s="6"/>
       <x:c r="H18" s="5" t="s">
-        <x:v>178</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="I18" s="5">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J18" s="5" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="19" customHeight="1">
       <x:c r="A19" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>181</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D19" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E19" s="6"/>
       <x:c r="F19" s="5"/>
-      <x:c r="G19" s="6"/>
+      <x:c r="G19" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="H19" s="5" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="I19" s="5" t="s">
-        <x:v>468</x:v>
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="I19" s="5">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J19" s="5" t="s">
-        <x:v>184</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="20" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>185</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>186</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
         <x:v>29</x:v>
@@ -6847,6 +6853,32 @@
         <x:v>468</x:v>
       </x:c>
       <x:c r="J20" s="5" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B21" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="I21" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="J21" t="s">
         <x:v>187</x:v>
       </x:c>
     </x:row>
@@ -7233,15 +7265,17 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
-        <x:v>506</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D8" s="6"/>
+      <x:c r="D8" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E8" s="6"/>
       <x:c r="F8" s="5" t="s">
-        <x:v>508</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G8" s="6" t="s">
         <x:v>137</x:v>
@@ -7257,22 +7291,20 @@
         <x:v>520</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
-        <x:v>466</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
-        <x:v>169</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E9" s="6"/>
-      <x:c r="F9" s="5" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H9" s="5"/>
+      <x:c r="F9" s="5"/>
+      <x:c r="G9" s="6"/>
+      <x:c r="H9" s="5">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
         <x:v>520</x:v>
@@ -7280,10 +7312,10 @@
     </x:row>
     <x:row r="10" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>521</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B10" s="5" t="s">
-        <x:v>522</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
         <x:v>161</x:v>
@@ -7293,33 +7325,29 @@
       </x:c>
       <x:c r="E10" s="6"/>
       <x:c r="F10" s="5"/>
-      <x:c r="G10" s="6"/>
-      <x:c r="H10" s="5">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G10" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5" t="s">
-        <x:v>521</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>159</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="B11" s="5" t="s">
-        <x:v>160</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C11" s="5" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="D11" s="6"/>
       <x:c r="E11" s="6"/>
       <x:c r="F11" s="5"/>
-      <x:c r="G11" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="G11" s="6"/>
       <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5" t="s">
@@ -7328,94 +7356,94 @@
     </x:row>
     <x:row r="12" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>524</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B12" s="5" t="s">
-        <x:v>277</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D12" s="6"/>
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="5"/>
       <x:c r="G12" s="6"/>
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5" t="s">
-        <x:v>524</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="13" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B13" s="5" t="s">
-        <x:v>293</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="D13" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="D13" s="6"/>
       <x:c r="E13" s="6"/>
       <x:c r="F13" s="5"/>
       <x:c r="G13" s="6"/>
       <x:c r="H13" s="5"/>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5" t="s">
-        <x:v>292</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="14" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>296</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B14" s="5" t="s">
-        <x:v>297</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="D14" s="6"/>
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E14" s="6"/>
       <x:c r="F14" s="5"/>
       <x:c r="G14" s="6"/>
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="5" t="s">
-        <x:v>296</x:v>
+        <x:v>524</x:v>
       </x:c>
     </x:row>
     <x:row r="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
-        <x:v>525</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B15" s="5" t="s">
-        <x:v>526</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
         <x:v>482</x:v>
       </x:c>
-      <x:c r="D15" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="D15" s="6"/>
       <x:c r="E15" s="6"/>
       <x:c r="F15" s="5"/>
       <x:c r="G15" s="6"/>
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5" t="s">
-        <x:v>525</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="16" customHeight="1">
       <x:c r="A16" s="5" t="s">
-        <x:v>480</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B16" s="5" t="s">
-        <x:v>481</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C16" s="5" t="s">
         <x:v>482</x:v>
@@ -7423,19 +7451,21 @@
       <x:c r="D16" s="6"/>
       <x:c r="E16" s="6"/>
       <x:c r="F16" s="5"/>
-      <x:c r="G16" s="6"/>
+      <x:c r="G16" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="H16" s="5"/>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="5" t="s">
-        <x:v>480</x:v>
+        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="17" customHeight="1">
       <x:c r="A17" s="5" t="s">
-        <x:v>485</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="B17" s="5" t="s">
-        <x:v>486</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C17" s="5" t="s">
         <x:v>482</x:v>
@@ -7443,21 +7473,19 @@
       <x:c r="D17" s="6"/>
       <x:c r="E17" s="6"/>
       <x:c r="F17" s="5"/>
-      <x:c r="G17" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="G17" s="6"/>
       <x:c r="H17" s="5"/>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="5" t="s">
-        <x:v>485</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="18" customHeight="1">
       <x:c r="A18" s="5" t="s">
-        <x:v>489</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="B18" s="5" t="s">
-        <x:v>490</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C18" s="5" t="s">
         <x:v>482</x:v>
@@ -7469,18 +7497,18 @@
       <x:c r="H18" s="5"/>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="5" t="s">
-        <x:v>489</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="19" customHeight="1">
       <x:c r="A19" s="5" t="s">
-        <x:v>493</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B19" s="5" t="s">
-        <x:v>527</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C19" s="5" t="s">
-        <x:v>482</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="D19" s="6"/>
       <x:c r="E19" s="6"/>
@@ -7489,35 +7517,37 @@
       <x:c r="H19" s="5"/>
       <x:c r="I19" s="5"/>
       <x:c r="J19" s="5" t="s">
-        <x:v>493</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="20" customHeight="1">
       <x:c r="A20" s="5" t="s">
-        <x:v>528</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B20" s="5" t="s">
-        <x:v>529</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C20" s="5" t="s">
-        <x:v>261</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D20" s="6"/>
       <x:c r="E20" s="6"/>
-      <x:c r="F20" s="5"/>
+      <x:c r="F20" s="5" t="s">
+        <x:v>170</x:v>
+      </x:c>
       <x:c r="G20" s="6"/>
       <x:c r="H20" s="5"/>
       <x:c r="I20" s="5"/>
       <x:c r="J20" s="5" t="s">
-        <x:v>528</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="21" customHeight="1">
       <x:c r="A21" s="5" t="s">
-        <x:v>167</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B21" s="5" t="s">
-        <x:v>168</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C21" s="5" t="s">
         <x:v>169</x:v>
@@ -7536,21 +7566,25 @@
     </x:row>
     <x:row r="22" customHeight="1">
       <x:c r="A22" s="5" t="s">
-        <x:v>173</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B22" s="5" t="s">
-        <x:v>174</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C22" s="5" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="D22" s="6"/>
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
       <x:c r="E22" s="6"/>
-      <x:c r="F22" s="5" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="G22" s="6"/>
-      <x:c r="H22" s="5"/>
+      <x:c r="F22" s="5"/>
+      <x:c r="G22" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="H22" s="5">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="I22" s="5"/>
       <x:c r="J22" s="5" t="s">
         <x:v>531</x:v>
@@ -7558,36 +7592,34 @@
     </x:row>
     <x:row r="23" customHeight="1">
       <x:c r="A23" s="5" t="s">
-        <x:v>176</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B23" s="5" t="s">
-        <x:v>177</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C23" s="5" t="s">
-        <x:v>161</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D23" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="E23" s="6"/>
       <x:c r="F23" s="5"/>
-      <x:c r="G23" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H23" s="5">
-        <x:v>0</x:v>
+      <x:c r="G23" s="6"/>
+      <x:c r="H23" s="5" t="s">
+        <x:v>182</x:v>
       </x:c>
       <x:c r="I23" s="5"/>
       <x:c r="J23" s="5" t="s">
-        <x:v>532</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="24" customHeight="1">
       <x:c r="A24" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B24" s="5" t="s">
-        <x:v>181</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C24" s="5" t="s">
         <x:v>29</x:v>
@@ -7603,32 +7635,20 @@
       </x:c>
       <x:c r="I24" s="5"/>
       <x:c r="J24" s="5" t="s">
-        <x:v>180</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="25" customHeight="1">
-      <x:c r="A25" s="5" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="B25" s="5" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="C25" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D25" s="6" t="s">
-        <x:v>137</x:v>
-      </x:c>
+      <x:c r="A25" s="5"/>
+      <x:c r="B25" s="5"/>
+      <x:c r="C25" s="5"/>
+      <x:c r="D25" s="6"/>
       <x:c r="E25" s="6"/>
       <x:c r="F25" s="5"/>
       <x:c r="G25" s="6"/>
-      <x:c r="H25" s="5" t="s">
-        <x:v>182</x:v>
-      </x:c>
+      <x:c r="H25" s="5"/>
       <x:c r="I25" s="5"/>
-      <x:c r="J25" s="5" t="s">
-        <x:v>185</x:v>
-      </x:c>
+      <x:c r="J25" s="5"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -8184,7 +8204,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R202202f0e73f46be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c944731bc64850"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8208,7 +8228,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>533</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -8275,12 +8295,12 @@
       <x:c r="H3" s="5"/>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="5" t="s">
-        <x:v>534</x:v>
+        <x:v>533</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>535</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
         <x:v>198</x:v>
@@ -8301,12 +8321,12 @@
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5" t="s">
-        <x:v>535</x:v>
+        <x:v>534</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>536</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>201</x:v>
@@ -8321,15 +8341,15 @@
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>536</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>537</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>538</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>169</x:v>
@@ -8337,7 +8357,7 @@
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
       <x:c r="F6" s="5" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="G6" s="6" t="s">
         <x:v>137</x:v>
@@ -8345,15 +8365,15 @@
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5" t="s">
-        <x:v>540</x:v>
+        <x:v>539</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>541</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
         <x:v>161</x:v>
@@ -8367,12 +8387,12 @@
       <x:c r="H7" s="5"/>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="5" t="s">
-        <x:v>541</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>506</x:v>
@@ -8391,15 +8411,15 @@
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>544</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>545</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>169</x:v>
@@ -8407,7 +8427,7 @@
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="5" t="s">
-        <x:v>546</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="G9" s="6" t="s">
         <x:v>137</x:v>
@@ -8415,7 +8435,7 @@
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>544</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
@@ -8757,7 +8777,7 @@
   <x:sheetData>
     <x:row r="1" s="7" customFormat="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -8803,10 +8823,10 @@
     </x:row>
     <x:row r="3" s="7" customFormat="1" customHeight="1">
       <x:c r="A3" s="5" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="s">
         <x:v>548</x:v>
-      </x:c>
-      <x:c r="B3" s="5" t="s">
-        <x:v>549</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
         <x:v>169</x:v>
@@ -8815,10 +8835,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
-        <x:v>539</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="G3" s="6" t="s">
         <x:v>137</x:v>
@@ -8826,7 +8846,7 @@
       <x:c r="H3" s="5"/>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="5" t="s">
-        <x:v>551</x:v>
+        <x:v>550</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="7" customFormat="1" customHeight="1">
@@ -8843,7 +8863,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E4" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
         <x:v>170</x:v>
@@ -8854,12 +8874,12 @@
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5" t="s">
-        <x:v>552</x:v>
+        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>240</x:v>
@@ -8878,7 +8898,7 @@
       </x:c>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>553</x:v>
+        <x:v>552</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8907,7 +8927,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -8974,15 +8994,15 @@
       <x:c r="H3" s="5"/>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="5" t="s">
-        <x:v>555</x:v>
+        <x:v>554</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>541</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>542</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>161</x:v>
@@ -8996,12 +9016,12 @@
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5" t="s">
-        <x:v>541</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>506</x:v>
@@ -9020,15 +9040,15 @@
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>543</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>544</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>545</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>169</x:v>
@@ -9036,7 +9056,7 @@
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
       <x:c r="F6" s="5" t="s">
-        <x:v>546</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="G6" s="6" t="s">
         <x:v>137</x:v>
@@ -9044,12 +9064,12 @@
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5" t="s">
-        <x:v>544</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
         <x:v>442</x:v>
@@ -9070,12 +9090,12 @@
       <x:c r="H7" s="5"/>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="5" t="s">
-        <x:v>556</x:v>
+        <x:v>555</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>557</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
         <x:v>201</x:v>
@@ -9090,15 +9110,15 @@
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5" t="s">
-        <x:v>557</x:v>
+        <x:v>556</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>558</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>559</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>169</x:v>
@@ -9116,15 +9136,15 @@
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>560</x:v>
+        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
       <x:c r="A10" s="5" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
         <x:v>561</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>562</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
         <x:v>161</x:v>
@@ -9140,7 +9160,7 @@
       <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5" t="s">
-        <x:v>563</x:v>
+        <x:v>562</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
@@ -9166,15 +9186,15 @@
       </x:c>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5" t="s">
-        <x:v>564</x:v>
+        <x:v>563</x:v>
       </x:c>
     </x:row>
     <x:row r="12" customHeight="1">
       <x:c r="A12" s="5" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="s">
         <x:v>565</x:v>
-      </x:c>
-      <x:c r="B12" s="5" t="s">
-        <x:v>566</x:v>
       </x:c>
       <x:c r="C12" s="5" t="s">
         <x:v>169</x:v>
@@ -9192,15 +9212,15 @@
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5" t="s">
-        <x:v>567</x:v>
+        <x:v>566</x:v>
       </x:c>
     </x:row>
     <x:row r="13" customHeight="1">
       <x:c r="A13" s="5" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="s">
         <x:v>568</x:v>
-      </x:c>
-      <x:c r="B13" s="5" t="s">
-        <x:v>569</x:v>
       </x:c>
       <x:c r="C13" s="5" t="s">
         <x:v>169</x:v>
@@ -9214,15 +9234,15 @@
       <x:c r="H13" s="5"/>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5" t="s">
-        <x:v>570</x:v>
+        <x:v>569</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26.399999618530273" customHeight="1">
       <x:c r="A14" s="5" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="s">
         <x:v>571</x:v>
-      </x:c>
-      <x:c r="B14" s="5" t="s">
-        <x:v>572</x:v>
       </x:c>
       <x:c r="C14" s="5" t="s">
         <x:v>482</x:v>
@@ -9234,15 +9254,15 @@
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="5" t="s">
-        <x:v>571</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="s">
         <x:v>573</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="s">
-        <x:v>574</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
         <x:v>482</x:v>
@@ -9254,7 +9274,7 @@
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5" t="s">
-        <x:v>573</x:v>
+        <x:v>572</x:v>
       </x:c>
     </x:row>
     <x:row r="16" customHeight="1">
@@ -9274,7 +9294,7 @@
       <x:c r="H16" s="5"/>
       <x:c r="I16" s="5"/>
       <x:c r="J16" s="5" t="s">
-        <x:v>575</x:v>
+        <x:v>574</x:v>
       </x:c>
     </x:row>
     <x:row r="17" customHeight="1">
@@ -9296,7 +9316,7 @@
       <x:c r="H17" s="5"/>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="18" customHeight="1">
@@ -9318,7 +9338,7 @@
       <x:c r="H18" s="5"/>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>530</x:v>
       </x:c>
     </x:row>
     <x:row r="19" customHeight="1">
@@ -9423,7 +9443,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>576</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -9494,12 +9514,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>577</x:v>
+        <x:v>576</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>578</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
         <x:v>506</x:v>
@@ -9524,15 +9544,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>579</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>580</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>581</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>298</x:v>
@@ -9549,18 +9569,18 @@
       </x:c>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="s">
         <x:v>582</x:v>
-      </x:c>
-      <x:c r="J5" s="5" t="s">
-        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>584</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>585</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>202</x:v>
@@ -9573,18 +9593,18 @@
       <x:c r="G6" s="6"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="J6" s="5" t="s">
-        <x:v>587</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>588</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>589</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
         <x:v>169</x:v>
@@ -9604,15 +9624,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>590</x:v>
+        <x:v>589</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
         <x:v>591</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>592</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
         <x:v>482</x:v>
@@ -9628,18 +9648,18 @@
         <x:v>494</x:v>
       </x:c>
       <x:c r="J8" s="5" t="s">
-        <x:v>593</x:v>
+        <x:v>592</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="s">
+      <x:c r="C9" s="5" t="s">
         <x:v>595</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
-        <x:v>596</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
         <x:v>137</x:v>
@@ -9652,15 +9672,15 @@
         <x:v>1000000</x:v>
       </x:c>
       <x:c r="J9" s="5" t="s">
-        <x:v>597</x:v>
+        <x:v>596</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
       <x:c r="A10" s="5" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="s">
-        <x:v>599</x:v>
       </x:c>
       <x:c r="C10" s="5" t="s">
         <x:v>261</x:v>
@@ -9673,10 +9693,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I10" s="5" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="J10" s="5" t="s">
         <x:v>600</x:v>
-      </x:c>
-      <x:c r="J10" s="5" t="s">
-        <x:v>601</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
@@ -9779,7 +9799,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J14" s="5" t="s">
         <x:v>184</x:v>
@@ -9805,7 +9825,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J15" s="5" t="s">
         <x:v>187</x:v>
@@ -9837,7 +9857,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>603</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -9908,15 +9928,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>604</x:v>
+        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>605</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>606</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>169</x:v>
@@ -9925,10 +9945,10 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E4" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>607</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G4" s="6" t="s">
         <x:v>137</x:v>
@@ -9938,15 +9958,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>608</x:v>
+        <x:v>607</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>609</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>610</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>298</x:v>
@@ -9955,7 +9975,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E5" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="6" t="s">
@@ -9963,21 +9983,21 @@
       </x:c>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="s">
         <x:v>611</x:v>
-      </x:c>
-      <x:c r="J5" s="5" t="s">
-        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>613</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>614</x:v>
-      </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>596</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D6" s="6" t="s">
         <x:v>137</x:v>
@@ -9990,7 +10010,7 @@
         <x:v>700000</x:v>
       </x:c>
       <x:c r="J6" s="5" t="s">
-        <x:v>615</x:v>
+        <x:v>614</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
@@ -10018,7 +10038,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>616</x:v>
+        <x:v>615</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
@@ -10121,7 +10141,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I11" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J11" s="5" t="s">
         <x:v>184</x:v>
@@ -10147,7 +10167,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
         <x:v>187</x:v>
@@ -10179,7 +10199,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>617</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -10250,15 +10270,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>618</x:v>
+        <x:v>617</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="26.399999618530273" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>619</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>620</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>169</x:v>
@@ -10268,7 +10288,7 @@
       </x:c>
       <x:c r="E4" s="6"/>
       <x:c r="F4" s="5" t="s">
-        <x:v>621</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="G4" s="6" t="s">
         <x:v>137</x:v>
@@ -10278,18 +10298,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>622</x:v>
+        <x:v>621</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>623</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>624</x:v>
-      </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>596</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
         <x:v>137</x:v>
@@ -10302,15 +10322,15 @@
         <x:v>200000</x:v>
       </x:c>
       <x:c r="J5" s="5" t="s">
-        <x:v>625</x:v>
+        <x:v>624</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>625</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>626</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>627</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>482</x:v>
@@ -10325,18 +10345,18 @@
       </x:c>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="s">
         <x:v>628</x:v>
-      </x:c>
-      <x:c r="J6" s="5" t="s">
-        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="7" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>630</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>631</x:v>
       </x:c>
       <x:c r="C7" s="5" t="s">
         <x:v>169</x:v>
@@ -10354,15 +10374,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>632</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>599</x:v>
       </x:c>
       <x:c r="C8" s="5" t="s">
         <x:v>261</x:v>
@@ -10375,10 +10395,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I8" s="5" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="J8" s="5" t="s">
         <x:v>633</x:v>
-      </x:c>
-      <x:c r="J8" s="5" t="s">
-        <x:v>634</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
@@ -10404,7 +10424,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J9" s="5" t="s">
-        <x:v>635</x:v>
+        <x:v>634</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
@@ -10481,10 +10501,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I12" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J12" s="5" t="s">
-        <x:v>636</x:v>
+        <x:v>635</x:v>
       </x:c>
     </x:row>
     <x:row r="13" customHeight="1">
@@ -10507,7 +10527,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I13" s="5" t="s">
-        <x:v>602</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="J13" s="5" t="s">
         <x:v>187</x:v>
@@ -10539,7 +10559,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -10610,15 +10630,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J3" s="5" t="s">
-        <x:v>638</x:v>
+        <x:v>637</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
         <x:v>605</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>606</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>169</x:v>
@@ -10628,7 +10648,7 @@
       </x:c>
       <x:c r="E4" s="6"/>
       <x:c r="F4" s="5" t="s">
-        <x:v>607</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="G4" s="6" t="s">
         <x:v>137</x:v>
@@ -10638,15 +10658,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>639</x:v>
+        <x:v>638</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>640</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>641</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>157</x:v>
@@ -10659,18 +10679,18 @@
       <x:c r="G5" s="6"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="s">
         <x:v>642</x:v>
-      </x:c>
-      <x:c r="J5" s="5" t="s">
-        <x:v>643</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
       <x:c r="A6" s="5" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="s">
         <x:v>644</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>645</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
         <x:v>157</x:v>
@@ -10687,21 +10707,21 @@
       </x:c>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="s">
         <x:v>646</x:v>
-      </x:c>
-      <x:c r="J6" s="5" t="s">
-        <x:v>647</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273" customHeight="1">
       <x:c r="A7" s="5" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
         <x:v>648</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="s">
+      <x:c r="C7" s="5" t="s">
         <x:v>649</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>650</x:v>
       </x:c>
       <x:c r="D7" s="6"/>
       <x:c r="E7" s="6"/>
@@ -10711,21 +10731,21 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="s">
         <x:v>651</x:v>
-      </x:c>
-      <x:c r="J7" s="5" t="s">
-        <x:v>652</x:v>
       </x:c>
     </x:row>
     <x:row r="8" customHeight="1">
       <x:c r="A8" s="5" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="s">
         <x:v>653</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="s">
+      <x:c r="C8" s="5" t="s">
         <x:v>654</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>655</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>137</x:v>
@@ -10735,18 +10755,18 @@
       <x:c r="G8" s="6"/>
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="J8" s="5" t="s">
         <x:v>656</x:v>
-      </x:c>
-      <x:c r="J8" s="5" t="s">
-        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="s">
         <x:v>658</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>659</x:v>
       </x:c>
       <x:c r="C9" s="5" t="s">
         <x:v>169</x:v>
@@ -10762,7 +10782,7 @@
         <x:v>102400</x:v>
       </x:c>
       <x:c r="J9" s="5" t="s">
-        <x:v>660</x:v>
+        <x:v>659</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
@@ -10790,7 +10810,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="5" t="s">
-        <x:v>661</x:v>
+        <x:v>660</x:v>
       </x:c>
     </x:row>
     <x:row r="11" customHeight="1">
@@ -10816,7 +10836,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="5" t="s">
-        <x:v>662</x:v>
+        <x:v>661</x:v>
       </x:c>
     </x:row>
     <x:row r="12" customHeight="1">
@@ -10893,10 +10913,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I14" s="5" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="J14" s="5" t="s">
         <x:v>663</x:v>
-      </x:c>
-      <x:c r="J14" s="5" t="s">
-        <x:v>664</x:v>
       </x:c>
     </x:row>
     <x:row r="15" customHeight="1">
@@ -10919,7 +10939,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="I15" s="5" t="s">
-        <x:v>663</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="J15" s="5" t="s">
         <x:v>187</x:v>
@@ -10951,7 +10971,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>665</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2"/>
@@ -11018,12 +11038,12 @@
       <x:c r="H3" s="5"/>
       <x:c r="I3" s="5"/>
       <x:c r="J3" s="5" t="s">
-        <x:v>666</x:v>
+        <x:v>665</x:v>
       </x:c>
     </x:row>
     <x:row r="4" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>519</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
         <x:v>506</x:v>
@@ -11046,7 +11066,7 @@
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5" t="s">
-        <x:v>519</x:v>
+        <x:v>666</x:v>
       </x:c>
     </x:row>
     <x:row r="5" customHeight="1">
@@ -11140,7 +11160,7 @@
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="9" customHeight="1">
@@ -11162,7 +11182,7 @@
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>530</x:v>
       </x:c>
     </x:row>
     <x:row r="10" customHeight="1">
@@ -11338,7 +11358,7 @@
         <x:v>672</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>620</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C4" s="5" t="s">
         <x:v>169</x:v>
@@ -11593,10 +11613,10 @@
     </x:row>
     <x:row r="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="s">
         <x:v>598</x:v>
-      </x:c>
-      <x:c r="B15" s="5" t="s">
-        <x:v>599</x:v>
       </x:c>
       <x:c r="C15" s="5" t="s">
         <x:v>261</x:v>
@@ -11608,7 +11628,7 @@
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5" t="s">
-        <x:v>598</x:v>
+        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="16" customHeight="1">
@@ -11656,7 +11676,7 @@
       <x:c r="H17" s="5"/>
       <x:c r="I17" s="5"/>
       <x:c r="J17" s="5" t="s">
-        <x:v>530</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="18" customHeight="1">
@@ -11678,7 +11698,7 @@
       <x:c r="H18" s="5"/>
       <x:c r="I18" s="5"/>
       <x:c r="J18" s="5" t="s">
-        <x:v>531</x:v>
+        <x:v>530</x:v>
       </x:c>
     </x:row>
     <x:row r="19" customHeight="1">
@@ -11837,7 +11857,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E3" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
         <x:v>690</x:v>
@@ -11865,7 +11885,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E4" s="6" t="s">
-        <x:v>550</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
         <x:v>170</x:v>
@@ -17792,30 +17812,32 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D155" s="14" t="str">
-        <x:v>负责人ID</x:v>
+        <x:v>所属需求ID</x:v>
       </x:c>
       <x:c r="E155" s="14" t="str">
-        <x:v>owner_id</x:v>
+        <x:v>requirement_id</x:v>
       </x:c>
       <x:c r="F155" s="14" t="str">
         <x:v>BIGINT</x:v>
       </x:c>
-      <x:c r="G155" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="H155" s="6"/>
+      <x:c r="G155" s="6"/>
+      <x:c r="H155" s="6" t="str">
+        <x:v>有效项目唯一</x:v>
+      </x:c>
       <x:c r="I155" s="6" t="str">
-        <x:v>pms_user.id</x:v>
+        <x:v>pms_requirement.id</x:v>
       </x:c>
       <x:c r="J155" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="K155" s="6"/>
+      <x:c r="K155" s="6" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
       <x:c r="L155" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="M155" s="14" t="str">
-        <x:v>项目负责人。</x:v>
+        <x:v>所属需求；历史数据可空，新建和编辑项目时必填。</x:v>
       </x:c>
       <x:c r="N155" s="14" t="str">
         <x:v>146</x:v>
@@ -17832,30 +17854,30 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D156" s="14" t="str">
-        <x:v>状态</x:v>
+        <x:v>负责人ID</x:v>
       </x:c>
       <x:c r="E156" s="14" t="str">
-        <x:v>status</x:v>
+        <x:v>owner_id</x:v>
       </x:c>
       <x:c r="F156" s="14" t="str">
-        <x:v>SMALLINT</x:v>
+        <x:v>BIGINT</x:v>
       </x:c>
       <x:c r="G156" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H156" s="6"/>
-      <x:c r="I156" s="6"/>
+      <x:c r="I156" s="6" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
       <x:c r="J156" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="K156" s="6" t="str">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K156" s="6"/>
       <x:c r="L156" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M156" s="14" t="str">
-        <x:v>0 未启动，1 进行中，2 已完成，3 暂停。</x:v>
+        <x:v>项目负责人。</x:v>
       </x:c>
       <x:c r="N156" s="14" t="str">
         <x:v>146</x:v>
@@ -17872,10 +17894,10 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D157" s="14" t="str">
-        <x:v>是否逾期</x:v>
+        <x:v>状态</x:v>
       </x:c>
       <x:c r="E157" s="14" t="str">
-        <x:v>is_overdue</x:v>
+        <x:v>status</x:v>
       </x:c>
       <x:c r="F157" s="14" t="str">
         <x:v>SMALLINT</x:v>
@@ -17895,7 +17917,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M157" s="14" t="str">
-        <x:v>0 未逾期，1 逾期。</x:v>
+        <x:v>0 未启动，1 进行中，2 已完成，3 暂停。</x:v>
       </x:c>
       <x:c r="N157" s="14" t="str">
         <x:v>146</x:v>
@@ -17912,26 +17934,30 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D158" s="14" t="str">
-        <x:v>启动日期</x:v>
+        <x:v>是否逾期</x:v>
       </x:c>
       <x:c r="E158" s="14" t="str">
-        <x:v>start_date</x:v>
+        <x:v>is_overdue</x:v>
       </x:c>
       <x:c r="F158" s="14" t="str">
-        <x:v>DATE</x:v>
-      </x:c>
-      <x:c r="G158" s="6"/>
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G158" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="H158" s="6"/>
       <x:c r="I158" s="6"/>
-      <x:c r="J158" s="6"/>
+      <x:c r="J158" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="K158" s="6" t="str">
-        <x:v>NULL</x:v>
-      </x:c>
-      <x:c r="L158" s="6" t="str">
-        <x:v>2026-07-11</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L158" s="6" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M158" s="14" t="str">
-        <x:v>项目启动日期。</x:v>
+        <x:v>0 未逾期，1 逾期。</x:v>
       </x:c>
       <x:c r="N158" s="14" t="str">
         <x:v>146</x:v>
@@ -17948,28 +17974,26 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D159" s="14" t="str">
-        <x:v>预计完成日期</x:v>
+        <x:v>启动日期</x:v>
       </x:c>
       <x:c r="E159" s="14" t="str">
-        <x:v>expected_end_date</x:v>
+        <x:v>start_date</x:v>
       </x:c>
       <x:c r="F159" s="14" t="str">
         <x:v>DATE</x:v>
       </x:c>
-      <x:c r="G159" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="G159" s="6"/>
       <x:c r="H159" s="6"/>
       <x:c r="I159" s="6"/>
-      <x:c r="J159" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="K159" s="6"/>
+      <x:c r="J159" s="6"/>
+      <x:c r="K159" s="6" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
       <x:c r="L159" s="6" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-07-11</x:v>
       </x:c>
       <x:c r="M159" s="14" t="str">
-        <x:v>预计完成日期。</x:v>
+        <x:v>项目启动日期。</x:v>
       </x:c>
       <x:c r="N159" s="14" t="str">
         <x:v>146</x:v>
@@ -17986,26 +18010,28 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D160" s="14" t="str">
-        <x:v>实际完成日期</x:v>
+        <x:v>预计完成日期</x:v>
       </x:c>
       <x:c r="E160" s="14" t="str">
-        <x:v>actual_end_date</x:v>
+        <x:v>expected_end_date</x:v>
       </x:c>
       <x:c r="F160" s="14" t="str">
         <x:v>DATE</x:v>
       </x:c>
-      <x:c r="G160" s="6"/>
+      <x:c r="G160" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="H160" s="6"/>
       <x:c r="I160" s="6"/>
-      <x:c r="J160" s="6"/>
-      <x:c r="K160" s="6" t="str">
-        <x:v>NULL</x:v>
-      </x:c>
+      <x:c r="J160" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K160" s="6"/>
       <x:c r="L160" s="6" t="str">
-        <x:v>2026-08-30</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="M160" s="14" t="str">
-        <x:v>实际完成日期。</x:v>
+        <x:v>预计完成日期。</x:v>
       </x:c>
       <x:c r="N160" s="14" t="str">
         <x:v>146</x:v>
@@ -18022,10 +18048,10 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D161" s="14" t="str">
-        <x:v>暂停日期</x:v>
+        <x:v>实际完成日期</x:v>
       </x:c>
       <x:c r="E161" s="14" t="str">
-        <x:v>suspend_date</x:v>
+        <x:v>actual_end_date</x:v>
       </x:c>
       <x:c r="F161" s="14" t="str">
         <x:v>DATE</x:v>
@@ -18038,10 +18064,10 @@
         <x:v>NULL</x:v>
       </x:c>
       <x:c r="L161" s="6" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-08-30</x:v>
       </x:c>
       <x:c r="M161" s="14" t="str">
-        <x:v>项目暂停日期。</x:v>
+        <x:v>实际完成日期。</x:v>
       </x:c>
       <x:c r="N161" s="14" t="str">
         <x:v>146</x:v>
@@ -18058,13 +18084,13 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D162" s="14" t="str">
-        <x:v>进度记录</x:v>
+        <x:v>暂停日期</x:v>
       </x:c>
       <x:c r="E162" s="14" t="str">
-        <x:v>progress_text</x:v>
+        <x:v>suspend_date</x:v>
       </x:c>
       <x:c r="F162" s="14" t="str">
-        <x:v>TEXT</x:v>
+        <x:v>DATE</x:v>
       </x:c>
       <x:c r="G162" s="6"/>
       <x:c r="H162" s="6"/>
@@ -18074,10 +18100,10 @@
         <x:v>NULL</x:v>
       </x:c>
       <x:c r="L162" s="6" t="str">
-        <x:v>按计划推进</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="M162" s="14" t="str">
-        <x:v>项目进度记录。</x:v>
+        <x:v>项目暂停日期。</x:v>
       </x:c>
       <x:c r="N162" s="14" t="str">
         <x:v>146</x:v>
@@ -18094,10 +18120,10 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D163" s="14" t="str">
-        <x:v>风险记录</x:v>
+        <x:v>进度记录</x:v>
       </x:c>
       <x:c r="E163" s="14" t="str">
-        <x:v>risk_text</x:v>
+        <x:v>progress_text</x:v>
       </x:c>
       <x:c r="F163" s="14" t="str">
         <x:v>TEXT</x:v>
@@ -18110,10 +18136,10 @@
         <x:v>NULL</x:v>
       </x:c>
       <x:c r="L163" s="6" t="str">
-        <x:v>暂无风险</x:v>
+        <x:v>按计划推进</x:v>
       </x:c>
       <x:c r="M163" s="14" t="str">
-        <x:v>项目风险记录。</x:v>
+        <x:v>项目进度记录。</x:v>
       </x:c>
       <x:c r="N163" s="14" t="str">
         <x:v>146</x:v>
@@ -18130,28 +18156,26 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D164" s="14" t="str">
-        <x:v>创建人ID</x:v>
+        <x:v>风险记录</x:v>
       </x:c>
       <x:c r="E164" s="14" t="str">
-        <x:v>creator_id</x:v>
+        <x:v>risk_text</x:v>
       </x:c>
       <x:c r="F164" s="14" t="str">
-        <x:v>BIGINT</x:v>
+        <x:v>TEXT</x:v>
       </x:c>
       <x:c r="G164" s="6"/>
       <x:c r="H164" s="6"/>
-      <x:c r="I164" s="6" t="str">
-        <x:v>pms_user.id</x:v>
-      </x:c>
+      <x:c r="I164" s="6"/>
       <x:c r="J164" s="6"/>
       <x:c r="K164" s="6" t="str">
         <x:v>NULL</x:v>
       </x:c>
-      <x:c r="L164" s="6" t="n">
-        <x:v>1</x:v>
+      <x:c r="L164" s="6" t="str">
+        <x:v>暂无风险</x:v>
       </x:c>
       <x:c r="M164" s="14" t="str">
-        <x:v>记录创建人。</x:v>
+        <x:v>项目风险记录。</x:v>
       </x:c>
       <x:c r="N164" s="14" t="str">
         <x:v>146</x:v>
@@ -18168,10 +18192,10 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D165" s="14" t="str">
-        <x:v>更新人ID</x:v>
+        <x:v>创建人ID</x:v>
       </x:c>
       <x:c r="E165" s="14" t="str">
-        <x:v>updater_id</x:v>
+        <x:v>creator_id</x:v>
       </x:c>
       <x:c r="F165" s="14" t="str">
         <x:v>BIGINT</x:v>
@@ -18189,7 +18213,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M165" s="14" t="str">
-        <x:v>记录最后更新人。</x:v>
+        <x:v>记录创建人。</x:v>
       </x:c>
       <x:c r="N165" s="14" t="str">
         <x:v>146</x:v>
@@ -18206,30 +18230,28 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D166" s="14" t="str">
-        <x:v>删除标记</x:v>
+        <x:v>更新人ID</x:v>
       </x:c>
       <x:c r="E166" s="14" t="str">
-        <x:v>is_deleted</x:v>
+        <x:v>updater_id</x:v>
       </x:c>
       <x:c r="F166" s="14" t="str">
-        <x:v>SMALLINT</x:v>
-      </x:c>
-      <x:c r="G166" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G166" s="6"/>
       <x:c r="H166" s="6"/>
-      <x:c r="I166" s="6"/>
-      <x:c r="J166" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="I166" s="6" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J166" s="6"/>
       <x:c r="K166" s="6" t="str">
-        <x:v>0</x:v>
+        <x:v>NULL</x:v>
       </x:c>
       <x:c r="L166" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M166" s="14" t="str">
-        <x:v>0 正常，1 删除。</x:v>
+        <x:v>记录最后更新人。</x:v>
       </x:c>
       <x:c r="N166" s="14" t="str">
         <x:v>146</x:v>
@@ -18246,28 +18268,30 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D167" s="14" t="str">
-        <x:v>创建时间</x:v>
+        <x:v>删除标记</x:v>
       </x:c>
       <x:c r="E167" s="14" t="str">
-        <x:v>created_at</x:v>
+        <x:v>is_deleted</x:v>
       </x:c>
       <x:c r="F167" s="14" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>SMALLINT</x:v>
       </x:c>
       <x:c r="G167" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H167" s="6"/>
       <x:c r="I167" s="6"/>
-      <x:c r="J167" s="6"/>
+      <x:c r="J167" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="K167" s="6" t="str">
-        <x:v>NOW()</x:v>
-      </x:c>
-      <x:c r="L167" s="6" t="str">
-        <x:v>2026-07-11 10:00:00</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L167" s="6" t="n">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M167" s="14" t="str">
-        <x:v>记录创建时间。</x:v>
+        <x:v>0 正常，1 删除。</x:v>
       </x:c>
       <x:c r="N167" s="14" t="str">
         <x:v>146</x:v>
@@ -18284,10 +18308,10 @@
         <x:v>项目表</x:v>
       </x:c>
       <x:c r="D168" s="14" t="str">
-        <x:v>更新时间</x:v>
+        <x:v>创建时间</x:v>
       </x:c>
       <x:c r="E168" s="14" t="str">
-        <x:v>updated_at</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="F168" s="14" t="str">
         <x:v>TIMESTAMPTZ</x:v>
@@ -18305,7 +18329,7 @@
         <x:v>2026-07-11 10:00:00</x:v>
       </x:c>
       <x:c r="M168" s="14" t="str">
-        <x:v>记录最后更新时间。</x:v>
+        <x:v>记录创建时间。</x:v>
       </x:c>
       <x:c r="N168" s="14" t="str">
         <x:v>146</x:v>
@@ -18316,38 +18340,34 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B169" s="14" t="str">
-        <x:v>pms_project_member</x:v>
+        <x:v>pms_project</x:v>
       </x:c>
       <x:c r="C169" s="14" t="str">
-        <x:v>项目成员表</x:v>
+        <x:v>项目表</x:v>
       </x:c>
       <x:c r="D169" s="14" t="str">
-        <x:v>主键ID</x:v>
+        <x:v>更新时间</x:v>
       </x:c>
       <x:c r="E169" s="14" t="str">
-        <x:v>id</x:v>
+        <x:v>updated_at</x:v>
       </x:c>
       <x:c r="F169" s="14" t="str">
-        <x:v>BIGSERIAL</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="G169" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="H169" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="H169" s="6"/>
       <x:c r="I169" s="6"/>
-      <x:c r="J169" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="J169" s="6"/>
       <x:c r="K169" s="6" t="str">
-        <x:v>自增</x:v>
-      </x:c>
-      <x:c r="L169" s="6" t="n">
-        <x:v>1</x:v>
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L169" s="6" t="str">
+        <x:v>2026-07-11 10:00:00</x:v>
       </x:c>
       <x:c r="M169" s="14" t="str">
-        <x:v>数据库主键。</x:v>
+        <x:v>记录最后更新时间。</x:v>
       </x:c>
       <x:c r="N169" s="14" t="str">
         <x:v>146</x:v>
@@ -18364,32 +18384,32 @@
         <x:v>项目成员表</x:v>
       </x:c>
       <x:c r="D170" s="14" t="str">
-        <x:v>项目ID</x:v>
+        <x:v>主键ID</x:v>
       </x:c>
       <x:c r="E170" s="14" t="str">
-        <x:v>project_id</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="F170" s="14" t="str">
-        <x:v>BIGINT</x:v>
+        <x:v>BIGSERIAL</x:v>
       </x:c>
       <x:c r="G170" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H170" s="6" t="str">
-        <x:v>联合唯一</x:v>
-      </x:c>
-      <x:c r="I170" s="6" t="str">
-        <x:v>pms_project.id</x:v>
-      </x:c>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I170" s="6"/>
       <x:c r="J170" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="K170" s="6"/>
+      <x:c r="K170" s="6" t="str">
+        <x:v>自增</x:v>
+      </x:c>
       <x:c r="L170" s="6" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="M170" s="14" t="str">
-        <x:v>所属项目，项目删除时级联删除。</x:v>
+        <x:v>数据库主键。</x:v>
       </x:c>
       <x:c r="N170" s="14" t="str">
         <x:v>146</x:v>
@@ -18406,10 +18426,10 @@
         <x:v>项目成员表</x:v>
       </x:c>
       <x:c r="D171" s="14" t="str">
-        <x:v>用户ID</x:v>
+        <x:v>项目ID</x:v>
       </x:c>
       <x:c r="E171" s="14" t="str">
-        <x:v>user_id</x:v>
+        <x:v>project_id</x:v>
       </x:c>
       <x:c r="F171" s="14" t="str">
         <x:v>BIGINT</x:v>
@@ -18421,17 +18441,17 @@
         <x:v>联合唯一</x:v>
       </x:c>
       <x:c r="I171" s="6" t="str">
-        <x:v>pms_user.id</x:v>
+        <x:v>pms_project.id</x:v>
       </x:c>
       <x:c r="J171" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="K171" s="6"/>
       <x:c r="L171" s="6" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M171" s="14" t="str">
-        <x:v>项目成员。</x:v>
+        <x:v>所属项目，项目删除时级联删除。</x:v>
       </x:c>
       <x:c r="N171" s="14" t="str">
         <x:v>146</x:v>
@@ -18448,28 +18468,32 @@
         <x:v>项目成员表</x:v>
       </x:c>
       <x:c r="D172" s="14" t="str">
-        <x:v>创建时间</x:v>
+        <x:v>用户ID</x:v>
       </x:c>
       <x:c r="E172" s="14" t="str">
-        <x:v>created_at</x:v>
+        <x:v>user_id</x:v>
       </x:c>
       <x:c r="F172" s="14" t="str">
-        <x:v>TIMESTAMPTZ</x:v>
+        <x:v>BIGINT</x:v>
       </x:c>
       <x:c r="G172" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="H172" s="6"/>
-      <x:c r="I172" s="6"/>
-      <x:c r="J172" s="6"/>
-      <x:c r="K172" s="6" t="str">
-        <x:v>NOW()</x:v>
-      </x:c>
-      <x:c r="L172" s="6" t="str">
-        <x:v>2026-07-11 10:00:00</x:v>
+      <x:c r="H172" s="6" t="str">
+        <x:v>联合唯一</x:v>
+      </x:c>
+      <x:c r="I172" s="6" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J172" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K172" s="6"/>
+      <x:c r="L172" s="6" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M172" s="14" t="str">
-        <x:v>成员加入时间。</x:v>
+        <x:v>项目成员。</x:v>
       </x:c>
       <x:c r="N172" s="14" t="str">
         <x:v>146</x:v>
@@ -18480,34 +18504,34 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="14" t="str">
-        <x:v>pms_requirement</x:v>
+        <x:v>pms_project_member</x:v>
       </x:c>
       <x:c r="C173" s="14" t="str">
-        <x:v>需求表</x:v>
+        <x:v>项目成员表</x:v>
       </x:c>
       <x:c r="D173" s="14" t="str">
-        <x:v>主键ID</x:v>
+        <x:v>创建时间</x:v>
       </x:c>
       <x:c r="E173" s="14" t="str">
-        <x:v>id</x:v>
+        <x:v>created_at</x:v>
       </x:c>
       <x:c r="F173" s="14" t="str">
-        <x:v>BIGSERIAL</x:v>
+        <x:v>TIMESTAMPTZ</x:v>
       </x:c>
       <x:c r="G173" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
-      <x:c r="H173" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="H173" s="6"/>
       <x:c r="I173" s="6"/>
-      <x:c r="J173" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="K173" s="6"/>
-      <x:c r="L173" s="6"/>
+      <x:c r="J173" s="6"/>
+      <x:c r="K173" s="6" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L173" s="6" t="str">
+        <x:v>2026-07-11 10:00:00</x:v>
+      </x:c>
       <x:c r="M173" s="14" t="str">
-        <x:v>需求 ID</x:v>
+        <x:v>成员加入时间。</x:v>
       </x:c>
       <x:c r="N173" s="14" t="str">
         <x:v>146</x:v>
@@ -18524,19 +18548,19 @@
         <x:v>需求表</x:v>
       </x:c>
       <x:c r="D174" s="14" t="str">
-        <x:v>需求标题</x:v>
+        <x:v>主键ID</x:v>
       </x:c>
       <x:c r="E174" s="14" t="str">
-        <x:v>title</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="F174" s="14" t="str">
-        <x:v>VARCHAR(200)</x:v>
+        <x:v>BIGSERIAL</x:v>
       </x:c>
       <x:c r="G174" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H174" s="6" t="str">
-        <x:v>有效数据唯一</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="I174" s="6"/>
       <x:c r="J174" s="6" t="str">
@@ -18545,7 +18569,7 @@
       <x:c r="K174" s="6"/>
       <x:c r="L174" s="6"/>
       <x:c r="M174" s="14" t="str">
-        <x:v>需求标题</x:v>
+        <x:v>需求 ID</x:v>
       </x:c>
       <x:c r="N174" s="14" t="str">
         <x:v>146</x:v>
@@ -18562,22 +18586,28 @@
         <x:v>需求表</x:v>
       </x:c>
       <x:c r="D175" s="14" t="str">
-        <x:v>富文本描述</x:v>
+        <x:v>需求标题</x:v>
       </x:c>
       <x:c r="E175" s="14" t="str">
-        <x:v>description</x:v>
+        <x:v>title</x:v>
       </x:c>
       <x:c r="F175" s="14" t="str">
-        <x:v>TEXT</x:v>
-      </x:c>
-      <x:c r="G175" s="6"/>
-      <x:c r="H175" s="6"/>
+        <x:v>VARCHAR(200)</x:v>
+      </x:c>
+      <x:c r="G175" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H175" s="6" t="str">
+        <x:v>有效数据唯一</x:v>
+      </x:c>
       <x:c r="I175" s="6"/>
-      <x:c r="J175" s="6"/>
+      <x:c r="J175" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="K175" s="6"/>
       <x:c r="L175" s="6"/>
       <x:c r="M175" s="14" t="str">
-        <x:v>富文本描述</x:v>
+        <x:v>需求标题</x:v>
       </x:c>
       <x:c r="N175" s="14" t="str">
         <x:v>146</x:v>
@@ -18594,26 +18624,22 @@
         <x:v>需求表</x:v>
       </x:c>
       <x:c r="D176" s="14" t="str">
-        <x:v>需求路径</x:v>
+        <x:v>富文本描述</x:v>
       </x:c>
       <x:c r="E176" s="14" t="str">
-        <x:v>requirement_type</x:v>
+        <x:v>description</x:v>
       </x:c>
       <x:c r="F176" s="14" t="str">
-        <x:v>SMALLINT</x:v>
-      </x:c>
-      <x:c r="G176" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+        <x:v>TEXT</x:v>
+      </x:c>
+      <x:c r="G176" s="6"/>
       <x:c r="H176" s="6"/>
       <x:c r="I176" s="6"/>
-      <x:c r="J176" s="6" t="str">
-        <x:v>是</x:v>
-      </x:c>
+      <x:c r="J176" s="6"/>
       <x:c r="K176" s="6"/>
       <x:c r="L176" s="6"/>
       <x:c r="M176" s="14" t="str">
-        <x:v>需求路径</x:v>
+        <x:v>富文本描述</x:v>
       </x:c>
       <x:c r="N176" s="14" t="str">
         <x:v>146</x:v>
@@ -18630,28 +18656,26 @@
         <x:v>需求表</x:v>
       </x:c>
       <x:c r="D177" s="14" t="str">
-        <x:v>所属产品</x:v>
+        <x:v>需求路径</x:v>
       </x:c>
       <x:c r="E177" s="14" t="str">
-        <x:v>product_id</x:v>
+        <x:v>requirement_type</x:v>
       </x:c>
       <x:c r="F177" s="14" t="str">
-        <x:v>BIGINT</x:v>
+        <x:v>SMALLINT</x:v>
       </x:c>
       <x:c r="G177" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="H177" s="6"/>
-      <x:c r="I177" s="6" t="str">
-        <x:v>pms_product.id</x:v>
-      </x:c>
+      <x:c r="I177" s="6"/>
       <x:c r="J177" s="6" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="K177" s="6"/>
       <x:c r="L177" s="6"/>
       <x:c r="M177" s="14" t="str">
-        <x:v>所属产品</x:v>
+        <x:v>需求路径</x:v>
       </x:c>
       <x:c r="N177" s="14" t="str">
         <x:v>146</x:v>
@@ -18668,18 +18692,20 @@
         <x:v>需求表</x:v>
       </x:c>
       <x:c r="D178" s="14" t="str">
-        <x:v>所属项目</x:v>
+        <x:v>所属产品</x:v>
       </x:c>
       <x:c r="E178" s="14" t="str">
-        <x:v>project_id</x:v>
+        <x:v>product_id</x:v>
       </x:c>
       <x:c r="F178" s="14" t="str">
         <x:v>BIGINT</x:v>
       </x:c>
-      <x:c r="G178" s="6"/>
+      <x:c r="G178" s="6" t="str">
+        <x:v>是</x:v>
+      </x:c>
       <x:c r="H178" s="6"/>
       <x:c r="I178" s="6" t="str">
-        <x:v>pms_project.id</x:v>
+        <x:v>pms_product.id</x:v>
       </x:c>
       <x:c r="J178" s="6" t="str">
         <x:v>是</x:v>
@@ -18687,7 +18713,7 @@
       <x:c r="K178" s="6"/>
       <x:c r="L178" s="6"/>
       <x:c r="M178" s="14" t="str">
-        <x:v>所属项目</x:v>
+        <x:v>所属产品</x:v>
       </x:c>
       <x:c r="N178" s="14" t="str">
         <x:v>146</x:v>
@@ -28786,7 +28812,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R084f4af7ceac4a29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ae4c486e2f941f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29143,10 +29169,10 @@
     </x:row>
     <x:row r="5" customHeight="1">
       <x:c r="A5" s="5" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="s">
         <x:v>640</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>641</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
         <x:v>157</x:v>
@@ -29160,7 +29186,7 @@
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>640</x:v>
+        <x:v>639</x:v>
       </x:c>
     </x:row>
     <x:row r="6" customHeight="1">
@@ -29220,10 +29246,10 @@
         <x:v>707</x:v>
       </x:c>
       <x:c r="B8" s="5" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="s">
         <x:v>654</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>655</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
         <x:v>137</x:v>
@@ -29239,7 +29265,7 @@
     </x:row>
     <x:row r="9" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>658</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B9" s="5" t="s">
         <x:v>708</x:v>
@@ -29256,7 +29282,7 @@
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5" t="s">
-        <x:v>658</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.399999618530273" customHeight="1">
@@ -29839,7 +29865,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14d483fafacf4591"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f4428bc8284d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30418,7 +30444,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0658cb8308c944af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7baecb9ba7784c82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30829,7 +30855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669ab833485d447d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cd416f05a6f4e3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31116,7 +31142,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c95d80f157e4959"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdacf2abfced6420c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31377,7 +31403,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Read8bbed9cfe4084"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70aca8ab9c614cbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31690,7 +31716,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R975fd239b14c4e0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86342a5b2fb24f4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/docs/数据库表结构.xlsx
+++ b/docs/数据库表结构.xlsx
@@ -2,46 +2,47 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R598066ce45924cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="Rdd9c21322ae04fe5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="Rdf73f606624840b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R9c1908b5c1ad40f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rbead0583b0a34b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R64edac48469141c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R533a277034614c62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R135a5ed9b44e493c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R52c522ba3c754310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="Rb1e653942f2e464d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="Rf4eba98ec4934d35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R626e2e597fb94408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="R45c5bd7daf0c4019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R032fa11a29a5415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R7c4c9e8ddda94d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="Rb8fe5200d2f04769"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rf437723395a14346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="R1ec50f03390048d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="R60272b4867ac455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="Rdbabbc26f65341d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="R9ac86962d16e45f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="R59af6c2c31dd4c3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="Re283412084f4486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="R98315dfe937b4cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="R4c8fe06484c9450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="Rbf8b40fcd31241e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="R8c389d0e09e1432a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R9c9ad31c92f74875"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="R4f0cda7b61344b44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="Rb577d4e39e134340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="Rb044f1b8c4184ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="Rce3d660fae8f4a80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R5fdf1fe74ca84e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R8d1e1fba1abb4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="R922ebf59939b4294"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="Rd8b54803a16e43a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="Re794dbf94cee42a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract" sheetId="38" r:id="R109b892c6215466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract_attachment" sheetId="39" r:id="Rd628293a55964965"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_scheduled_task_execution" sheetId="40" r:id="R6336962012ac460c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设计规则" sheetId="1" r:id="R5000a7eecfbe4481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表清单" sheetId="2" r:id="R0d254a0a70514fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段汇总" sheetId="31" r:id="Rc6716c3430b74a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user" sheetId="3" r:id="R212e55bf7fd24c6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role" sheetId="4" r:id="Rb5b63bb5eac34717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_role" sheetId="5" r:id="R4a512cfa369c4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_menu" sheetId="6" r:id="R0f12c807b88a4b91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_role_menu" sheetId="7" r:id="R6790a607e89f4ef9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_work_order" sheetId="8" r:id="R8ba5481a28fc4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive_type" sheetId="9" r:id="R18ebed75314949dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_archive" sheetId="10" r:id="R7c66f246d1ad4c27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_op_log" sheetId="11" r:id="R9f4b0b09b1044a34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_access_log" sheetId="12" r:id="Ra31ea2163cea491d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_user_preference" sheetId="13" r:id="R2e6afab358b14360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_message" sheetId="14" r:id="R848f608d8efb4278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product" sheetId="15" r:id="R3127cff3f47e4f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project" sheetId="16" r:id="Rcc51760466834866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_member" sheetId="17" r:id="Rbb109a6401e4467a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_requirement" sheetId="18" r:id="R0219e179713d4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task" sheetId="19" r:id="R206b317edcd64488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_task_owner" sheetId="30" r:id="Rc01e3c2f769f43f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_bug" sheetId="20" r:id="Ra2a1269325ce49dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract" sheetId="21" r:id="R732f72744c1b4bac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_stage" sheetId="22" r:id="Rd8258a7ba78f4019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_payment_record" sheetId="23" r:id="Rb5ecc719bbaf4a27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_contract_attachment" sheetId="24" r:id="Rf73cb7a197ad471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_stage" sheetId="25" r:id="Race7eec57b6145aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item" sheetId="26" r:id="R4b00abf9684c44c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_item_collabora" sheetId="27" r:id="Rba9fb8d93c944350"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_adjustment" sheetId="28" r:id="R4ffa7946df074689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_delivery_file" sheetId="29" r:id="R69e1f59bfa5d40fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_client" sheetId="32" r:id="R07ba1c15991f4af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_audit_log" sheetId="33" r:id="R0fcb9ce808c7469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_mcp_action_ticket" sheetId="34" r:id="R70b830c748314ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template" sheetId="35" r:id="R42b81986d5284972"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_stage" sheetId="36" r:id="R9019d348fea54bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_project_plan_template_item" sheetId="37" r:id="Rc45cf8c3add346af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract" sheetId="38" r:id="R198ba0b47e944094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_product_maintenance_contract_attachment" sheetId="39" r:id="R0b42ace4768248ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_scheduled_task_execution" sheetId="40" r:id="R25f318667ac94904"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pms_business_attachment" sheetId="41" r:id="Rfe883cb351fd46bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2299,7 +2300,7 @@
       <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
-  <x:fills count="39">
+  <x:fills count="41">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -2489,6 +2490,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFC5E8F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF5B9BD5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -2810,7 +2821,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="47">
+  <x:cellXfs count="63">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
@@ -2927,6 +2938,38 @@
     <x:xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="25" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="40" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -8136,10 +8179,24 @@
         <x:v>通用定时任务幂等、执行状态、重试和结果记录。</x:v>
       </x:c>
     </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>需求、项目、任务、BUG、运维工单的 OSS 附件元数据。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0db8c70f3a894476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb4ad46dd0034b54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28784,6 +28841,540 @@
         <x:v>NOT NULL</x:v>
       </x:c>
     </x:row>
+    <x:row r="453">
+      <x:c r="A453" t="n">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B453" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C453" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D453" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="E453" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="F453" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="G453" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H453" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I453"/>
+      <x:c r="J453" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K453" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="L453" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M453" t="str">
+        <x:v>附件主键。</x:v>
+      </x:c>
+      <x:c r="N453" t="str">
+        <x:v>PRIMARY KEY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454">
+      <x:c r="A454" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B454" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C454" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D454" t="str">
+        <x:v>业务类型</x:v>
+      </x:c>
+      <x:c r="E454" t="str">
+        <x:v>business_type</x:v>
+      </x:c>
+      <x:c r="F454" t="str">
+        <x:v>VARCHAR(30)</x:v>
+      </x:c>
+      <x:c r="G454" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H454"/>
+      <x:c r="I454"/>
+      <x:c r="J454" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K454"/>
+      <x:c r="L454" t="str">
+        <x:v>task</x:v>
+      </x:c>
+      <x:c r="M454" t="str">
+        <x:v>requirement、project、task、bug 或 work_order。</x:v>
+      </x:c>
+      <x:c r="N454" t="str">
+        <x:v>CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455">
+      <x:c r="A455" t="n">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B455" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C455" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D455" t="str">
+        <x:v>业务记录ID</x:v>
+      </x:c>
+      <x:c r="E455" t="str">
+        <x:v>business_id</x:v>
+      </x:c>
+      <x:c r="F455" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G455" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H455"/>
+      <x:c r="I455"/>
+      <x:c r="J455" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K455"/>
+      <x:c r="L455" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M455" t="str">
+        <x:v>多态关联的业务记录主键，不设置物理外键。</x:v>
+      </x:c>
+      <x:c r="N455" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456">
+      <x:c r="A456" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B456" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C456" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D456" t="str">
+        <x:v>原文件名</x:v>
+      </x:c>
+      <x:c r="E456" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="F456" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="G456" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H456"/>
+      <x:c r="I456"/>
+      <x:c r="J456"/>
+      <x:c r="K456"/>
+      <x:c r="L456" t="str">
+        <x:v>需求说明书.pdf</x:v>
+      </x:c>
+      <x:c r="M456" t="str">
+        <x:v>上传时的原文件名。</x:v>
+      </x:c>
+      <x:c r="N456" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457">
+      <x:c r="A457" t="n">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B457" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C457" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D457" t="str">
+        <x:v>文件类型</x:v>
+      </x:c>
+      <x:c r="E457" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="F457" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="G457" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H457"/>
+      <x:c r="I457"/>
+      <x:c r="J457"/>
+      <x:c r="K457"/>
+      <x:c r="L457" t="str">
+        <x:v>application/pdf</x:v>
+      </x:c>
+      <x:c r="M457" t="str">
+        <x:v>文件 MIME 类型。</x:v>
+      </x:c>
+      <x:c r="N457" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458">
+      <x:c r="A458" t="n">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B458" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C458" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D458" t="str">
+        <x:v>文件大小</x:v>
+      </x:c>
+      <x:c r="E458" t="str">
+        <x:v>file_size</x:v>
+      </x:c>
+      <x:c r="F458" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G458" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H458"/>
+      <x:c r="I458"/>
+      <x:c r="J458"/>
+      <x:c r="K458"/>
+      <x:c r="L458" t="str">
+        <x:v>102400</x:v>
+      </x:c>
+      <x:c r="M458" t="str">
+        <x:v>单位字节；大于 0 且不超过 20971520。</x:v>
+      </x:c>
+      <x:c r="N458" t="str">
+        <x:v>CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459">
+      <x:c r="A459" t="n">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B459" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C459" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D459" t="str">
+        <x:v>OSS存储键</x:v>
+      </x:c>
+      <x:c r="E459" t="str">
+        <x:v>storage_key</x:v>
+      </x:c>
+      <x:c r="F459" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="G459" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H459" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="I459"/>
+      <x:c r="J459" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K459"/>
+      <x:c r="L459" t="str">
+        <x:v>business/task/80/file.pdf</x:v>
+      </x:c>
+      <x:c r="M459" t="str">
+        <x:v>OSS 文件路径。</x:v>
+      </x:c>
+      <x:c r="N459" t="str">
+        <x:v>UNIQUE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460">
+      <x:c r="A460" t="n">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B460" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C460" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D460" t="str">
+        <x:v>OSS响应</x:v>
+      </x:c>
+      <x:c r="E460" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="F460" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="G460" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H460"/>
+      <x:c r="I460"/>
+      <x:c r="J460"/>
+      <x:c r="K460"/>
+      <x:c r="L460" t="str">
+        <x:v>{"code":100,"msg":"success"}</x:v>
+      </x:c>
+      <x:c r="M460" t="str">
+        <x:v>OSS 上传接口返回的完整 JSON。</x:v>
+      </x:c>
+      <x:c r="N460" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" t="n">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B461" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C461" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D461" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="E461" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="F461" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="G461" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H461"/>
+      <x:c r="I461"/>
+      <x:c r="J461" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K461" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L461" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M461" t="str">
+        <x:v>同一业务记录附件的显示顺序。</x:v>
+      </x:c>
+      <x:c r="N461" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462">
+      <x:c r="A462" t="n">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B462" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C462" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D462" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="E462" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="F462" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G462"/>
+      <x:c r="H462"/>
+      <x:c r="I462" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J462"/>
+      <x:c r="K462" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L462" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M462" t="str">
+        <x:v>记录上传人。</x:v>
+      </x:c>
+      <x:c r="N462" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463">
+      <x:c r="A463" t="n">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B463" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C463" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D463" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="E463" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="F463" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="G463"/>
+      <x:c r="H463"/>
+      <x:c r="I463" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="J463"/>
+      <x:c r="K463" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="L463" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M463" t="str">
+        <x:v>记录最后更新人。</x:v>
+      </x:c>
+      <x:c r="N463" t="str">
+        <x:v>ON DELETE SET NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464">
+      <x:c r="A464" t="n">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B464" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C464" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D464" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="E464" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="F464" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="G464" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H464"/>
+      <x:c r="I464"/>
+      <x:c r="J464" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="K464" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L464" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M464" t="str">
+        <x:v>0 正常，1 删除。</x:v>
+      </x:c>
+      <x:c r="N464" t="str">
+        <x:v>CHECK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465">
+      <x:c r="A465" t="n">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B465" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C465" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D465" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="E465" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="F465" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G465" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H465"/>
+      <x:c r="I465"/>
+      <x:c r="J465"/>
+      <x:c r="K465" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L465" t="str">
+        <x:v>2026-08-19 10:00:00</x:v>
+      </x:c>
+      <x:c r="M465" t="str">
+        <x:v>记录上传时间。</x:v>
+      </x:c>
+      <x:c r="N465" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466">
+      <x:c r="A466" t="n">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B466" t="str">
+        <x:v>pms_business_attachment</x:v>
+      </x:c>
+      <x:c r="C466" t="str">
+        <x:v>通用业务附件表</x:v>
+      </x:c>
+      <x:c r="D466" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="E466" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="F466" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="G466" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H466"/>
+      <x:c r="I466"/>
+      <x:c r="J466"/>
+      <x:c r="K466" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="L466" t="str">
+        <x:v>2026-08-19 10:00:00</x:v>
+      </x:c>
+      <x:c r="M466" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+      <x:c r="N466" t="str">
+        <x:v>NOT NULL</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:N1"/>
@@ -28791,7 +29382,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd93456aa2b41450a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf906115616944d4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29844,7 +30435,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36e13a02e6434a8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4683fc36d0a14fe6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30423,7 +31014,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62afc60774d440a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7869814ef0984dee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30834,7 +31425,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R250f19950842412e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59ab38faf32542d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31121,7 +31712,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cfa3d3255294c21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4112073f8304b78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31382,7 +31973,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4803bc6d4d6a408f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcde7d7b1a56b4657"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31695,7 +32286,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c9ddf630ee4bc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R380c3df128e64975"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33485,6 +34076,442 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17.780000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.890000343322754" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.110000610351562" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.329999923706055" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24.440000534057617" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="47.779998779296875" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="51" t="str">
+        <x:v>pms_business_attachment（通用业务附件表）</x:v>
+      </x:c>
+      <x:c r="B1" s="51"/>
+      <x:c r="C1" s="51"/>
+      <x:c r="D1" s="51"/>
+      <x:c r="E1" s="51"/>
+      <x:c r="F1" s="51"/>
+      <x:c r="G1" s="51"/>
+      <x:c r="H1" s="51"/>
+      <x:c r="I1" s="51"/>
+      <x:c r="J1" s="51"/>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="57" t="str">
+        <x:v>中文字段名</x:v>
+      </x:c>
+      <x:c r="B2" s="57" t="str">
+        <x:v>技术字段名</x:v>
+      </x:c>
+      <x:c r="C2" s="57" t="str">
+        <x:v>数据类型</x:v>
+      </x:c>
+      <x:c r="D2" s="57" t="str">
+        <x:v>必填</x:v>
+      </x:c>
+      <x:c r="E2" s="57" t="str">
+        <x:v>是否唯一</x:v>
+      </x:c>
+      <x:c r="F2" s="57" t="str">
+        <x:v>关联引用</x:v>
+      </x:c>
+      <x:c r="G2" s="57" t="str">
+        <x:v>是否索引</x:v>
+      </x:c>
+      <x:c r="H2" s="57" t="str">
+        <x:v>默认值</x:v>
+      </x:c>
+      <x:c r="I2" s="57" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="J2" s="57" t="str">
+        <x:v>字段说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="62" t="str">
+        <x:v>主键ID</x:v>
+      </x:c>
+      <x:c r="B3" s="62" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C3" s="62" t="str">
+        <x:v>BIGSERIAL</x:v>
+      </x:c>
+      <x:c r="D3" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E3" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F3" s="62"/>
+      <x:c r="G3" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H3" s="62" t="str">
+        <x:v>自增</x:v>
+      </x:c>
+      <x:c r="I3" s="62" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="62" t="str">
+        <x:v>附件主键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="62" t="str">
+        <x:v>业务类型</x:v>
+      </x:c>
+      <x:c r="B4" s="62" t="str">
+        <x:v>business_type</x:v>
+      </x:c>
+      <x:c r="C4" s="62" t="str">
+        <x:v>VARCHAR(30)</x:v>
+      </x:c>
+      <x:c r="D4" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E4" s="62"/>
+      <x:c r="F4" s="62"/>
+      <x:c r="G4" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H4" s="62"/>
+      <x:c r="I4" s="62" t="str">
+        <x:v>task</x:v>
+      </x:c>
+      <x:c r="J4" s="62" t="str">
+        <x:v>requirement、project、task、bug 或 work_order。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="62" t="str">
+        <x:v>业务记录ID</x:v>
+      </x:c>
+      <x:c r="B5" s="62" t="str">
+        <x:v>business_id</x:v>
+      </x:c>
+      <x:c r="C5" s="62" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D5" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E5" s="62"/>
+      <x:c r="F5" s="62"/>
+      <x:c r="G5" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H5" s="62"/>
+      <x:c r="I5" s="62" t="str">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J5" s="62" t="str">
+        <x:v>多态关联的业务记录主键，不设置物理外键。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="62" t="str">
+        <x:v>原文件名</x:v>
+      </x:c>
+      <x:c r="B6" s="62" t="str">
+        <x:v>original_name</x:v>
+      </x:c>
+      <x:c r="C6" s="62" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D6" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E6" s="62"/>
+      <x:c r="F6" s="62"/>
+      <x:c r="G6" s="62"/>
+      <x:c r="H6" s="62"/>
+      <x:c r="I6" s="62" t="str">
+        <x:v>需求说明书.pdf</x:v>
+      </x:c>
+      <x:c r="J6" s="62" t="str">
+        <x:v>上传时的原文件名。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="62" t="str">
+        <x:v>文件类型</x:v>
+      </x:c>
+      <x:c r="B7" s="62" t="str">
+        <x:v>mime_type</x:v>
+      </x:c>
+      <x:c r="C7" s="62" t="str">
+        <x:v>VARCHAR(150)</x:v>
+      </x:c>
+      <x:c r="D7" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E7" s="62"/>
+      <x:c r="F7" s="62"/>
+      <x:c r="G7" s="62"/>
+      <x:c r="H7" s="62"/>
+      <x:c r="I7" s="62" t="str">
+        <x:v>application/pdf</x:v>
+      </x:c>
+      <x:c r="J7" s="62" t="str">
+        <x:v>文件 MIME 类型。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="62" t="str">
+        <x:v>文件大小</x:v>
+      </x:c>
+      <x:c r="B8" s="62" t="str">
+        <x:v>file_size</x:v>
+      </x:c>
+      <x:c r="C8" s="62" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D8" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E8" s="62"/>
+      <x:c r="F8" s="62"/>
+      <x:c r="G8" s="62"/>
+      <x:c r="H8" s="62"/>
+      <x:c r="I8" s="62" t="str">
+        <x:v>102400</x:v>
+      </x:c>
+      <x:c r="J8" s="62" t="str">
+        <x:v>单位字节；大于 0 且不超过 20971520。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="62" t="str">
+        <x:v>OSS存储键</x:v>
+      </x:c>
+      <x:c r="B9" s="62" t="str">
+        <x:v>storage_key</x:v>
+      </x:c>
+      <x:c r="C9" s="62" t="str">
+        <x:v>VARCHAR(255)</x:v>
+      </x:c>
+      <x:c r="D9" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E9" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F9" s="62"/>
+      <x:c r="G9" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H9" s="62"/>
+      <x:c r="I9" s="62" t="str">
+        <x:v>business/task/80/file.pdf</x:v>
+      </x:c>
+      <x:c r="J9" s="62" t="str">
+        <x:v>OSS 文件路径。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="62" t="str">
+        <x:v>OSS响应</x:v>
+      </x:c>
+      <x:c r="B10" s="62" t="str">
+        <x:v>oss_response</x:v>
+      </x:c>
+      <x:c r="C10" s="62" t="str">
+        <x:v>JSONB</x:v>
+      </x:c>
+      <x:c r="D10" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E10" s="62"/>
+      <x:c r="F10" s="62"/>
+      <x:c r="G10" s="62"/>
+      <x:c r="H10" s="62"/>
+      <x:c r="I10" s="62" t="str">
+        <x:v>{"code":100,"msg":"success"}</x:v>
+      </x:c>
+      <x:c r="J10" s="62" t="str">
+        <x:v>OSS 上传接口返回的完整 JSON。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="62" t="str">
+        <x:v>排序号</x:v>
+      </x:c>
+      <x:c r="B11" s="62" t="str">
+        <x:v>sort_order</x:v>
+      </x:c>
+      <x:c r="C11" s="62" t="str">
+        <x:v>INTEGER</x:v>
+      </x:c>
+      <x:c r="D11" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E11" s="62"/>
+      <x:c r="F11" s="62"/>
+      <x:c r="G11" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H11" s="62" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="62" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J11" s="62" t="str">
+        <x:v>同一业务记录附件的显示顺序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="62" t="str">
+        <x:v>创建人ID</x:v>
+      </x:c>
+      <x:c r="B12" s="62" t="str">
+        <x:v>creator_id</x:v>
+      </x:c>
+      <x:c r="C12" s="62" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D12" s="62"/>
+      <x:c r="E12" s="62"/>
+      <x:c r="F12" s="62" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G12" s="62"/>
+      <x:c r="H12" s="62" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I12" s="62" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="62" t="str">
+        <x:v>记录上传人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="62" t="str">
+        <x:v>更新人ID</x:v>
+      </x:c>
+      <x:c r="B13" s="62" t="str">
+        <x:v>updater_id</x:v>
+      </x:c>
+      <x:c r="C13" s="62" t="str">
+        <x:v>BIGINT</x:v>
+      </x:c>
+      <x:c r="D13" s="62"/>
+      <x:c r="E13" s="62"/>
+      <x:c r="F13" s="62" t="str">
+        <x:v>pms_user.id</x:v>
+      </x:c>
+      <x:c r="G13" s="62"/>
+      <x:c r="H13" s="62" t="str">
+        <x:v>NULL</x:v>
+      </x:c>
+      <x:c r="I13" s="62" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="62" t="str">
+        <x:v>记录最后更新人。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="62" t="str">
+        <x:v>删除标记</x:v>
+      </x:c>
+      <x:c r="B14" s="62" t="str">
+        <x:v>is_deleted</x:v>
+      </x:c>
+      <x:c r="C14" s="62" t="str">
+        <x:v>SMALLINT</x:v>
+      </x:c>
+      <x:c r="D14" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E14" s="62"/>
+      <x:c r="F14" s="62"/>
+      <x:c r="G14" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="H14" s="62" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" s="62" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J14" s="62" t="str">
+        <x:v>0 正常，1 删除。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="62" t="str">
+        <x:v>创建时间</x:v>
+      </x:c>
+      <x:c r="B15" s="62" t="str">
+        <x:v>created_at</x:v>
+      </x:c>
+      <x:c r="C15" s="62" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D15" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E15" s="62"/>
+      <x:c r="F15" s="62"/>
+      <x:c r="G15" s="62"/>
+      <x:c r="H15" s="62" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I15" s="62" t="str">
+        <x:v>2026-08-19 10:00:00</x:v>
+      </x:c>
+      <x:c r="J15" s="62" t="str">
+        <x:v>记录上传时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="62" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+      <x:c r="B16" s="62" t="str">
+        <x:v>updated_at</x:v>
+      </x:c>
+      <x:c r="C16" s="62" t="str">
+        <x:v>TIMESTAMPTZ</x:v>
+      </x:c>
+      <x:c r="D16" s="62" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="E16" s="62"/>
+      <x:c r="F16" s="62"/>
+      <x:c r="G16" s="62"/>
+      <x:c r="H16" s="62" t="str">
+        <x:v>NOW()</x:v>
+      </x:c>
+      <x:c r="I16" s="62" t="str">
+        <x:v>2026-08-19 10:00:00</x:v>
+      </x:c>
+      <x:c r="J16" s="62" t="str">
+        <x:v>记录最后更新时间。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
